--- a/wiki/comparisons/출하현황_납품처별_월별분석_2026.xlsx
+++ b/wiki/comparisons/출하현황_납품처별_월별분석_2026.xlsx
@@ -95,7 +95,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -156,11 +156,32 @@
       <top style="thin"/>
       <bottom style="thin"/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="43">
+  <cellXfs count="44">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -286,6 +307,7 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -651,7 +673,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:P72"/>
+  <dimension ref="A1:P73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -792,7 +814,7 @@
         <v>493</v>
       </c>
       <c r="J3" s="26" t="n">
-        <v>0</v>
+        <v>107</v>
       </c>
       <c r="K3" s="26" t="n">
         <v>0</v>
@@ -811,7 +833,7 @@
         <v/>
       </c>
       <c r="P3" s="28">
-        <f>O3/O$72</f>
+        <f>O3/O$73</f>
         <v/>
       </c>
     </row>
@@ -846,7 +868,7 @@
         <v>433</v>
       </c>
       <c r="J4" s="26" t="n">
-        <v>0</v>
+        <v>29</v>
       </c>
       <c r="K4" s="26" t="n">
         <v>0</v>
@@ -865,7 +887,7 @@
         <v/>
       </c>
       <c r="P4" s="28">
-        <f>O4/O$72</f>
+        <f>O4/O$73</f>
         <v/>
       </c>
     </row>
@@ -900,7 +922,7 @@
         <v>183</v>
       </c>
       <c r="J5" s="26" t="n">
-        <v>0</v>
+        <v>77</v>
       </c>
       <c r="K5" s="26" t="n">
         <v>0</v>
@@ -919,7 +941,7 @@
         <v/>
       </c>
       <c r="P5" s="28">
-        <f>O5/O$72</f>
+        <f>O5/O$73</f>
         <v/>
       </c>
     </row>
@@ -973,7 +995,7 @@
         <v/>
       </c>
       <c r="P6" s="28">
-        <f>O6/O$72</f>
+        <f>O6/O$73</f>
         <v/>
       </c>
     </row>
@@ -1008,7 +1030,7 @@
         <v>35</v>
       </c>
       <c r="J7" s="26" t="n">
-        <v>0</v>
+        <v>16</v>
       </c>
       <c r="K7" s="26" t="n">
         <v>0</v>
@@ -1027,3533 +1049,3587 @@
         <v/>
       </c>
       <c r="P7" s="28">
-        <f>O7/O$72</f>
+        <f>O7/O$73</f>
         <v/>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="29" t="n">
+      <c r="A8" s="24" t="n">
         <v>6</v>
       </c>
-      <c r="B8" s="30" t="inlineStr">
+      <c r="B8" s="25" t="inlineStr">
         <is>
           <t>덕원종합상사</t>
         </is>
       </c>
-      <c r="C8" s="31" t="n">
+      <c r="C8" s="26" t="n">
         <v>69</v>
       </c>
-      <c r="D8" s="31" t="n">
+      <c r="D8" s="26" t="n">
         <v>110</v>
       </c>
-      <c r="E8" s="31" t="n">
+      <c r="E8" s="26" t="n">
         <v>75</v>
       </c>
-      <c r="F8" s="31" t="n">
+      <c r="F8" s="26" t="n">
         <v>138</v>
       </c>
-      <c r="G8" s="31" t="n">
+      <c r="G8" s="26" t="n">
         <v>62</v>
       </c>
-      <c r="H8" s="31" t="n">
+      <c r="H8" s="26" t="n">
         <v>69</v>
       </c>
-      <c r="I8" s="31" t="n">
+      <c r="I8" s="26" t="n">
         <v>116</v>
       </c>
-      <c r="J8" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L8" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M8" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N8" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O8" s="32">
+      <c r="J8" s="26" t="n">
+        <v>107</v>
+      </c>
+      <c r="K8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" s="27">
         <f>SUM(C8:N8)</f>
         <v/>
       </c>
-      <c r="P8" s="33">
-        <f>O8/O$72</f>
+      <c r="P8" s="28">
+        <f>O8/O$73</f>
         <v/>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="29" t="n">
+      <c r="A9" s="24" t="n">
         <v>7</v>
       </c>
-      <c r="B9" s="30" t="inlineStr">
+      <c r="B9" s="25" t="inlineStr">
         <is>
           <t>연성기공(주)</t>
         </is>
       </c>
-      <c r="C9" s="31" t="n">
+      <c r="C9" s="26" t="n">
         <v>7</v>
       </c>
-      <c r="D9" s="31" t="n">
+      <c r="D9" s="26" t="n">
         <v>88</v>
       </c>
-      <c r="E9" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="31" t="n">
+      <c r="E9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="26" t="n">
         <v>56</v>
       </c>
-      <c r="G9" s="31" t="n">
+      <c r="G9" s="26" t="n">
         <v>192</v>
       </c>
-      <c r="H9" s="31" t="n">
+      <c r="H9" s="26" t="n">
         <v>121</v>
       </c>
-      <c r="I9" s="31" t="n">
+      <c r="I9" s="26" t="n">
         <v>139</v>
       </c>
-      <c r="J9" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K9" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L9" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M9" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N9" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O9" s="32">
+      <c r="J9" s="26" t="n">
+        <v>23</v>
+      </c>
+      <c r="K9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" s="27">
         <f>SUM(C9:N9)</f>
         <v/>
       </c>
-      <c r="P9" s="33">
-        <f>O9/O$72</f>
+      <c r="P9" s="28">
+        <f>O9/O$73</f>
         <v/>
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="29" t="n">
+      <c r="A10" s="24" t="n">
         <v>8</v>
       </c>
-      <c r="B10" s="30" t="inlineStr">
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>아신상사</t>
+        </is>
+      </c>
+      <c r="C10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D10" s="26" t="n">
+        <v>134</v>
+      </c>
+      <c r="E10" s="26" t="n">
+        <v>152</v>
+      </c>
+      <c r="F10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H10" s="26" t="n">
+        <v>138</v>
+      </c>
+      <c r="I10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J10" s="26" t="n">
+        <v>155</v>
+      </c>
+      <c r="K10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" s="27">
+        <f>SUM(C10:N10)</f>
+        <v/>
+      </c>
+      <c r="P10" s="28">
+        <f>O10/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
         <is>
           <t>영우툴링(창성툴)</t>
         </is>
       </c>
-      <c r="C10" s="31" t="n">
+      <c r="C11" s="26" t="n">
         <v>159</v>
       </c>
-      <c r="D10" s="31" t="n">
+      <c r="D11" s="26" t="n">
         <v>72</v>
       </c>
-      <c r="E10" s="31" t="n">
+      <c r="E11" s="26" t="n">
         <v>34</v>
       </c>
-      <c r="F10" s="31" t="n">
+      <c r="F11" s="26" t="n">
         <v>41</v>
       </c>
-      <c r="G10" s="31" t="n">
+      <c r="G11" s="26" t="n">
         <v>66</v>
       </c>
-      <c r="H10" s="31" t="n">
+      <c r="H11" s="26" t="n">
         <v>57</v>
       </c>
-      <c r="I10" s="31" t="n">
+      <c r="I11" s="26" t="n">
         <v>109</v>
       </c>
-      <c r="J10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N10" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O10" s="32">
-        <f>SUM(C10:N10)</f>
-        <v/>
-      </c>
-      <c r="P10" s="33">
-        <f>O10/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="29" t="n">
+      <c r="J11" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="K11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" s="27">
+        <f>SUM(C11:N11)</f>
+        <v/>
+      </c>
+      <c r="P11" s="28">
+        <f>O11/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>아이티공구</t>
+        </is>
+      </c>
+      <c r="C12" s="26" t="n">
+        <v>61</v>
+      </c>
+      <c r="D12" s="26" t="n">
+        <v>83</v>
+      </c>
+      <c r="E12" s="26" t="n">
+        <v>43</v>
+      </c>
+      <c r="F12" s="26" t="n">
+        <v>41</v>
+      </c>
+      <c r="G12" s="26" t="n">
+        <v>118</v>
+      </c>
+      <c r="H12" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="I12" s="26" t="n">
+        <v>128</v>
+      </c>
+      <c r="J12" s="26" t="n">
+        <v>67</v>
+      </c>
+      <c r="K12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" s="27">
+        <f>SUM(C12:N12)</f>
+        <v/>
+      </c>
+      <c r="P12" s="28">
+        <f>O12/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>유비툴</t>
+        </is>
+      </c>
+      <c r="C13" s="26" t="n">
+        <v>38</v>
+      </c>
+      <c r="D13" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="E13" s="26" t="n">
+        <v>53</v>
+      </c>
+      <c r="F13" s="26" t="n">
+        <v>53</v>
+      </c>
+      <c r="G13" s="26" t="n">
+        <v>182</v>
+      </c>
+      <c r="H13" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="I13" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="J13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" s="27">
+        <f>SUM(C13:N13)</f>
+        <v/>
+      </c>
+      <c r="P13" s="28">
+        <f>O13/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>(주)공화공구</t>
+        </is>
+      </c>
+      <c r="C14" s="26" t="n">
+        <v>66</v>
+      </c>
+      <c r="D14" s="26" t="n">
+        <v>47</v>
+      </c>
+      <c r="E14" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="F14" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="G14" s="26" t="n">
+        <v>34</v>
+      </c>
+      <c r="H14" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="I14" s="26" t="n">
+        <v>90</v>
+      </c>
+      <c r="J14" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="K14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N14" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O14" s="27">
+        <f>SUM(C14:N14)</f>
+        <v/>
+      </c>
+      <c r="P14" s="28">
+        <f>O14/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>신우툴링(남동)</t>
+        </is>
+      </c>
+      <c r="C15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E15" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="F15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G15" s="26" t="n">
+        <v>190</v>
+      </c>
+      <c r="H15" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="I15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J15" s="26" t="n">
+        <v>67</v>
+      </c>
+      <c r="K15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N15" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O15" s="27">
+        <f>SUM(C15:N15)</f>
+        <v/>
+      </c>
+      <c r="P15" s="28">
+        <f>O15/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>알제이코리아</t>
+        </is>
+      </c>
+      <c r="C16" s="26" t="n">
+        <v>64</v>
+      </c>
+      <c r="D16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="F16" s="26" t="n">
+        <v>75</v>
+      </c>
+      <c r="G16" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="H16" s="26" t="n">
+        <v>58</v>
+      </c>
+      <c r="I16" s="26" t="n">
+        <v>35</v>
+      </c>
+      <c r="J16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N16" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O16" s="27">
+        <f>SUM(C16:N16)</f>
+        <v/>
+      </c>
+      <c r="P16" s="28">
+        <f>O16/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>반석공구</t>
+        </is>
+      </c>
+      <c r="C17" s="26" t="n">
+        <v>32</v>
+      </c>
+      <c r="D17" s="26" t="n">
+        <v>22</v>
+      </c>
+      <c r="E17" s="26" t="n">
+        <v>28</v>
+      </c>
+      <c r="F17" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="G17" s="26" t="n">
+        <v>85</v>
+      </c>
+      <c r="H17" s="26" t="n">
+        <v>56</v>
+      </c>
+      <c r="I17" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="J17" s="26" t="n">
+        <v>59</v>
+      </c>
+      <c r="K17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N17" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O17" s="27">
+        <f>SUM(C17:N17)</f>
+        <v/>
+      </c>
+      <c r="P17" s="28">
+        <f>O17/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>왕삼아공구</t>
+        </is>
+      </c>
+      <c r="C18" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="D18" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="E18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F18" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="G18" s="26" t="n">
+        <v>156</v>
+      </c>
+      <c r="H18" s="26" t="n">
+        <v>54</v>
+      </c>
+      <c r="I18" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="J18" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N18" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O18" s="27">
+        <f>SUM(C18:N18)</f>
+        <v/>
+      </c>
+      <c r="P18" s="28">
+        <f>O18/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>대륙기계공구</t>
+        </is>
+      </c>
+      <c r="C19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E19" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="F19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G19" s="26" t="n">
+        <v>60</v>
+      </c>
+      <c r="H19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="I19" s="26" t="n">
+        <v>158</v>
+      </c>
+      <c r="J19" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="K19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N19" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O19" s="27">
+        <f>SUM(C19:N19)</f>
+        <v/>
+      </c>
+      <c r="P19" s="28">
+        <f>O19/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>(주)금형티에스</t>
+        </is>
+      </c>
+      <c r="C20" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="D20" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="E20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F20" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="G20" s="26" t="n">
+        <v>145</v>
+      </c>
+      <c r="H20" s="26" t="n">
+        <v>74</v>
+      </c>
+      <c r="I20" s="26" t="n">
         <v>9</v>
       </c>
-      <c r="B11" s="30" t="inlineStr">
-        <is>
-          <t>아이티공구</t>
-        </is>
-      </c>
-      <c r="C11" s="31" t="n">
+      <c r="J20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N20" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O20" s="27">
+        <f>SUM(C20:N20)</f>
+        <v/>
+      </c>
+      <c r="P20" s="28">
+        <f>O20/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>(주)세종종합상사(미산동)</t>
+        </is>
+      </c>
+      <c r="C21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G21" s="26" t="n">
+        <v>64</v>
+      </c>
+      <c r="H21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="26" t="n">
+        <v>134</v>
+      </c>
+      <c r="J21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N21" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O21" s="27">
+        <f>SUM(C21:N21)</f>
+        <v/>
+      </c>
+      <c r="P21" s="28">
+        <f>O21/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>케이엠툴링</t>
+        </is>
+      </c>
+      <c r="C22" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="D22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E22" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="F22" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="G22" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="H22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="26" t="n">
+        <v>81</v>
+      </c>
+      <c r="J22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N22" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O22" s="27">
+        <f>SUM(C22:N22)</f>
+        <v/>
+      </c>
+      <c r="P22" s="28">
+        <f>O22/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>핫몰드엔지니어링주식회사-코고툴(재연마)</t>
+        </is>
+      </c>
+      <c r="C23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="26" t="n">
+        <v>79</v>
+      </c>
+      <c r="F23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="26" t="n">
+        <v>52</v>
+      </c>
+      <c r="I23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J23" s="26" t="n">
+        <v>57</v>
+      </c>
+      <c r="K23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N23" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O23" s="27">
+        <f>SUM(C23:N23)</f>
+        <v/>
+      </c>
+      <c r="P23" s="28">
+        <f>O23/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>서림툴링</t>
+        </is>
+      </c>
+      <c r="C24" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="D24" s="26" t="n">
+        <v>42</v>
+      </c>
+      <c r="E24" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="F24" s="26" t="n">
+        <v>36</v>
+      </c>
+      <c r="G24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="26" t="n">
+        <v>27</v>
+      </c>
+      <c r="I24" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="J24" s="26" t="n">
+        <v>18</v>
+      </c>
+      <c r="K24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N24" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O24" s="27">
+        <f>SUM(C24:N24)</f>
+        <v/>
+      </c>
+      <c r="P24" s="28">
+        <f>O24/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>동명ENG-코고툴(재연마)</t>
+        </is>
+      </c>
+      <c r="C25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H25" s="26" t="n">
+        <v>84</v>
+      </c>
+      <c r="I25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J25" s="26" t="n">
+        <v>86</v>
+      </c>
+      <c r="K25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N25" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O25" s="27">
+        <f>SUM(C25:N25)</f>
+        <v/>
+      </c>
+      <c r="P25" s="28">
+        <f>O25/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>지니툴(구로)_코고툴</t>
+        </is>
+      </c>
+      <c r="C26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H26" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="I26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J26" s="26" t="n">
+        <v>116</v>
+      </c>
+      <c r="K26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N26" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O26" s="27">
+        <f>SUM(C26:N26)</f>
+        <v/>
+      </c>
+      <c r="P26" s="28">
+        <f>O26/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>대우툴링</t>
+        </is>
+      </c>
+      <c r="C27" s="26" t="n">
+        <v>60</v>
+      </c>
+      <c r="D27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E27" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G27" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="H27" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="I27" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="J27" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="K27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N27" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O27" s="27">
+        <f>SUM(C27:N27)</f>
+        <v/>
+      </c>
+      <c r="P27" s="28">
+        <f>O27/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>이엠티(EMT)</t>
+        </is>
+      </c>
+      <c r="C28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D28" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="E28" s="26" t="n">
+        <v>104</v>
+      </c>
+      <c r="F28" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G28" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="H28" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N28" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O28" s="27">
+        <f>SUM(C28:N28)</f>
+        <v/>
+      </c>
+      <c r="P28" s="28">
+        <f>O28/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>영창툴링</t>
+        </is>
+      </c>
+      <c r="C29" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="D29" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="E29" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="F29" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="G29" s="26" t="n">
+        <v>26</v>
+      </c>
+      <c r="H29" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="I29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N29" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O29" s="27">
+        <f>SUM(C29:N29)</f>
+        <v/>
+      </c>
+      <c r="P29" s="28">
+        <f>O29/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>다영툴링</t>
+        </is>
+      </c>
+      <c r="C30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D30" s="26" t="n">
+        <v>82</v>
+      </c>
+      <c r="E30" s="26" t="n">
+        <v>17</v>
+      </c>
+      <c r="F30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N30" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O30" s="27">
+        <f>SUM(C30:N30)</f>
+        <v/>
+      </c>
+      <c r="P30" s="28">
+        <f>O30/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>유성상공사</t>
+        </is>
+      </c>
+      <c r="C31" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="D31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E31" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="F31" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="G31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H31" s="26" t="n">
+        <v>73</v>
+      </c>
+      <c r="I31" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N31" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O31" s="27">
+        <f>SUM(C31:N31)</f>
+        <v/>
+      </c>
+      <c r="P31" s="28">
+        <f>O31/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>스마트툴스</t>
+        </is>
+      </c>
+      <c r="C32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E32" s="26" t="n">
+        <v>95</v>
+      </c>
+      <c r="F32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N32" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O32" s="27">
+        <f>SUM(C32:N32)</f>
+        <v/>
+      </c>
+      <c r="P32" s="28">
+        <f>O32/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>E-tech(이테크)</t>
+        </is>
+      </c>
+      <c r="C33" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="D33" s="26" t="n">
+        <v>44</v>
+      </c>
+      <c r="E33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="J33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N33" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O33" s="27">
+        <f>SUM(C33:N33)</f>
+        <v/>
+      </c>
+      <c r="P33" s="28">
+        <f>O33/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>(주)정원테크</t>
+        </is>
+      </c>
+      <c r="C34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D34" s="26" t="n">
+        <v>50</v>
+      </c>
+      <c r="E34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G34" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="H34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J34" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="K34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N34" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O34" s="27">
+        <f>SUM(C34:N34)</f>
+        <v/>
+      </c>
+      <c r="P34" s="28">
+        <f>O34/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>광진테크</t>
+        </is>
+      </c>
+      <c r="C35" s="26" t="n">
+        <v>37</v>
+      </c>
+      <c r="D35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E35" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F35" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="G35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H35" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="I35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J35" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="K35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N35" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O35" s="27">
+        <f>SUM(C35:N35)</f>
+        <v/>
+      </c>
+      <c r="P35" s="28">
+        <f>O35/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>뉴툴(New tool)</t>
+        </is>
+      </c>
+      <c r="C36" s="26" t="n">
+        <v>70</v>
+      </c>
+      <c r="D36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N36" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O36" s="27">
+        <f>SUM(C36:N36)</f>
+        <v/>
+      </c>
+      <c r="P36" s="28">
+        <f>O36/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>(주)전진공구</t>
+        </is>
+      </c>
+      <c r="C37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H37" s="26" t="n">
+        <v>53</v>
+      </c>
+      <c r="I37" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J37" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="K37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N37" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O37" s="27">
+        <f>SUM(C37:N37)</f>
+        <v/>
+      </c>
+      <c r="P37" s="28">
+        <f>O37/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="24" t="n">
+        <v>36</v>
+      </c>
+      <c r="B38" s="25" t="inlineStr">
+        <is>
+          <t>(주)일등정밀공구(안산)</t>
+        </is>
+      </c>
+      <c r="C38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D38" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="E38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G38" s="26" t="n">
+        <v>45</v>
+      </c>
+      <c r="H38" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="I38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N38" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O38" s="27">
+        <f>SUM(C38:N38)</f>
+        <v/>
+      </c>
+      <c r="P38" s="28">
+        <f>O38/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="24" t="n">
+        <v>37</v>
+      </c>
+      <c r="B39" s="25" t="inlineStr">
+        <is>
+          <t>맨날툴이야</t>
+        </is>
+      </c>
+      <c r="C39" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="D39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E39" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="F39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G39" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="H39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="J39" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="K39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N39" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O39" s="27">
+        <f>SUM(C39:N39)</f>
+        <v/>
+      </c>
+      <c r="P39" s="28">
+        <f>O39/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="24" t="n">
+        <v>38</v>
+      </c>
+      <c r="B40" s="25" t="inlineStr">
+        <is>
+          <t>공구백화점(미산동)</t>
+        </is>
+      </c>
+      <c r="C40" s="26" t="n">
+        <v>16</v>
+      </c>
+      <c r="D40" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="E40" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="F40" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="G40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H40" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="I40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J40" s="26" t="n">
+        <v>25</v>
+      </c>
+      <c r="K40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N40" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O40" s="27">
+        <f>SUM(C40:N40)</f>
+        <v/>
+      </c>
+      <c r="P40" s="28">
+        <f>O40/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="24" t="n">
+        <v>39</v>
+      </c>
+      <c r="B41" s="25" t="inlineStr">
+        <is>
+          <t>예일공구상사</t>
+        </is>
+      </c>
+      <c r="C41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E41" s="26" t="n">
+        <v>57</v>
+      </c>
+      <c r="F41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N41" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O41" s="27">
+        <f>SUM(C41:N41)</f>
+        <v/>
+      </c>
+      <c r="P41" s="28">
+        <f>O41/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="24" t="n">
+        <v>40</v>
+      </c>
+      <c r="B42" s="25" t="inlineStr">
+        <is>
+          <t>하나테크</t>
+        </is>
+      </c>
+      <c r="C42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F42" s="26" t="n">
+        <v>39</v>
+      </c>
+      <c r="G42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H42" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I42" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N42" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O42" s="27">
+        <f>SUM(C42:N42)</f>
+        <v/>
+      </c>
+      <c r="P42" s="28">
+        <f>O42/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="24" t="n">
+        <v>41</v>
+      </c>
+      <c r="B43" s="25" t="inlineStr">
+        <is>
+          <t>(주)바로공구(정남)</t>
+        </is>
+      </c>
+      <c r="C43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E43" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="26" t="n">
+        <v>21</v>
+      </c>
+      <c r="J43" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="K43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N43" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O43" s="27">
+        <f>SUM(C43:N43)</f>
+        <v/>
+      </c>
+      <c r="P43" s="28">
+        <f>O43/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="24" t="n">
+        <v>42</v>
+      </c>
+      <c r="B44" s="25" t="inlineStr">
+        <is>
+          <t>대성테크</t>
+        </is>
+      </c>
+      <c r="C44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F44" s="26" t="n">
+        <v>29</v>
+      </c>
+      <c r="G44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H44" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="I44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N44" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O44" s="27">
+        <f>SUM(C44:N44)</f>
+        <v/>
+      </c>
+      <c r="P44" s="28">
+        <f>O44/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="24" t="n">
+        <v>43</v>
+      </c>
+      <c r="B45" s="25" t="inlineStr">
+        <is>
+          <t>인코테크 포승</t>
+        </is>
+      </c>
+      <c r="C45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="26" t="n">
+        <v>40</v>
+      </c>
+      <c r="J45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N45" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O45" s="27">
+        <f>SUM(C45:N45)</f>
+        <v/>
+      </c>
+      <c r="P45" s="28">
+        <f>O45/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="24" t="n">
+        <v>44</v>
+      </c>
+      <c r="B46" s="25" t="inlineStr">
+        <is>
+          <t>유진상사(문래)</t>
+        </is>
+      </c>
+      <c r="C46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D46" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G46" s="26" t="n">
+        <v>19</v>
+      </c>
+      <c r="H46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="J46" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="K46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N46" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O46" s="27">
+        <f>SUM(C46:N46)</f>
+        <v/>
+      </c>
+      <c r="P46" s="28">
+        <f>O46/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="24" t="n">
+        <v>45</v>
+      </c>
+      <c r="B47" s="25" t="inlineStr">
+        <is>
+          <t>대명종합공구-코고툴(재연마)</t>
+        </is>
+      </c>
+      <c r="C47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D47" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="E47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F47" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="G47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H47" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="I47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N47" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O47" s="27">
+        <f>SUM(C47:N47)</f>
+        <v/>
+      </c>
+      <c r="P47" s="28">
+        <f>O47/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="24" t="n">
+        <v>46</v>
+      </c>
+      <c r="B48" s="25" t="inlineStr">
+        <is>
+          <t>신우툴스</t>
+        </is>
+      </c>
+      <c r="C48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="J48" s="26" t="n">
+        <v>20</v>
+      </c>
+      <c r="K48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N48" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O48" s="27">
+        <f>SUM(C48:N48)</f>
+        <v/>
+      </c>
+      <c r="P48" s="28">
+        <f>O48/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="24" t="n">
+        <v>47</v>
+      </c>
+      <c r="B49" s="25" t="inlineStr">
+        <is>
+          <t>영호종합공구(향남)</t>
+        </is>
+      </c>
+      <c r="C49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H49" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="I49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J49" s="26" t="n">
+        <v>24</v>
+      </c>
+      <c r="K49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N49" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O49" s="27">
+        <f>SUM(C49:N49)</f>
+        <v/>
+      </c>
+      <c r="P49" s="28">
+        <f>O49/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="24" t="n">
+        <v>48</v>
+      </c>
+      <c r="B50" s="25" t="inlineStr">
+        <is>
+          <t>(주)코리아테크닉스</t>
+        </is>
+      </c>
+      <c r="C50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E50" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="F50" s="26" t="n">
+        <v>15</v>
+      </c>
+      <c r="G50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N50" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O50" s="27">
+        <f>SUM(C50:N50)</f>
+        <v/>
+      </c>
+      <c r="P50" s="28">
+        <f>O50/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="24" t="n">
+        <v>49</v>
+      </c>
+      <c r="B51" s="25" t="inlineStr">
+        <is>
+          <t>공구공구</t>
+        </is>
+      </c>
+      <c r="C51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G51" s="26" t="n">
+        <v>30</v>
+      </c>
+      <c r="H51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N51" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O51" s="27">
+        <f>SUM(C51:N51)</f>
+        <v/>
+      </c>
+      <c r="P51" s="28">
+        <f>O51/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="24" t="n">
+        <v>50</v>
+      </c>
+      <c r="B52" s="25" t="inlineStr">
+        <is>
+          <t>유성종합공구</t>
+        </is>
+      </c>
+      <c r="C52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D52" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="E52" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G52" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="H52" s="26" t="n">
+        <v>5</v>
+      </c>
+      <c r="I52" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="J52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N52" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O52" s="27">
+        <f>SUM(C52:N52)</f>
+        <v/>
+      </c>
+      <c r="P52" s="28">
+        <f>O52/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="24" t="n">
+        <v>51</v>
+      </c>
+      <c r="B53" s="25" t="inlineStr">
+        <is>
+          <t>대양공구(인천)</t>
+        </is>
+      </c>
+      <c r="C53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F53" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="G53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J53" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N53" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O53" s="27">
+        <f>SUM(C53:N53)</f>
+        <v/>
+      </c>
+      <c r="P53" s="28">
+        <f>O53/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="24" t="n">
+        <v>52</v>
+      </c>
+      <c r="B54" s="25" t="inlineStr">
+        <is>
+          <t>코끼리공구</t>
+        </is>
+      </c>
+      <c r="C54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G54" s="26" t="n">
+        <v>3</v>
+      </c>
+      <c r="H54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="26" t="n">
+        <v>13</v>
+      </c>
+      <c r="J54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N54" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O54" s="27">
+        <f>SUM(C54:N54)</f>
+        <v/>
+      </c>
+      <c r="P54" s="28">
+        <f>O54/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="24" t="n">
+        <v>53</v>
+      </c>
+      <c r="B55" s="25" t="inlineStr">
+        <is>
+          <t>(주)두영</t>
+        </is>
+      </c>
+      <c r="C55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D55" s="26" t="n">
+        <v>14</v>
+      </c>
+      <c r="E55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N55" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O55" s="27">
+        <f>SUM(C55:N55)</f>
+        <v/>
+      </c>
+      <c r="P55" s="28">
+        <f>O55/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="24" t="n">
+        <v>54</v>
+      </c>
+      <c r="B56" s="25" t="inlineStr">
+        <is>
+          <t>N.T.S(엔티에스)-코고툴</t>
+        </is>
+      </c>
+      <c r="C56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G56" s="26" t="n">
+        <v>12</v>
+      </c>
+      <c r="H56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N56" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O56" s="27">
+        <f>SUM(C56:N56)</f>
+        <v/>
+      </c>
+      <c r="P56" s="28">
+        <f>O56/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="24" t="n">
+        <v>55</v>
+      </c>
+      <c r="B57" s="25" t="inlineStr">
+        <is>
+          <t>(주)금천종합공구(독산)</t>
+        </is>
+      </c>
+      <c r="C57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E57" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="F57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G57" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="H57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N57" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O57" s="27">
+        <f>SUM(C57:N57)</f>
+        <v/>
+      </c>
+      <c r="P57" s="28">
+        <f>O57/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="24" t="n">
+        <v>56</v>
+      </c>
+      <c r="B58" s="25" t="inlineStr">
+        <is>
+          <t>세운상사</t>
+        </is>
+      </c>
+      <c r="C58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F58" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="G58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H58" s="26" t="n">
+        <v>11</v>
+      </c>
+      <c r="I58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N58" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O58" s="27">
+        <f>SUM(C58:N58)</f>
+        <v/>
+      </c>
+      <c r="P58" s="28">
+        <f>O58/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="24" t="n">
+        <v>57</v>
+      </c>
+      <c r="B59" s="25" t="inlineStr">
+        <is>
+          <t>웰크리에이트-코고툴(재연마)</t>
+        </is>
+      </c>
+      <c r="C59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="G59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J59" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="K59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N59" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O59" s="27">
+        <f>SUM(C59:N59)</f>
+        <v/>
+      </c>
+      <c r="P59" s="28">
+        <f>O59/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="24" t="n">
+        <v>58</v>
+      </c>
+      <c r="B60" s="25" t="inlineStr">
+        <is>
+          <t>(주)성환공구</t>
+        </is>
+      </c>
+      <c r="C60" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="D60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E60" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="G60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J60" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="K60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N60" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O60" s="27">
+        <f>SUM(C60:N60)</f>
+        <v/>
+      </c>
+      <c r="P60" s="28">
+        <f>O60/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="24" t="n">
+        <v>59</v>
+      </c>
+      <c r="B61" s="25" t="inlineStr">
+        <is>
+          <t>아시아툴링</t>
+        </is>
+      </c>
+      <c r="C61" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D61" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E61" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F61" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G61" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H61" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J61" s="26" t="n">
+        <v>10</v>
+      </c>
+      <c r="K61" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L61" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M61" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N61" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O61" s="27">
+        <f>SUM(C61:N61)</f>
+        <v/>
+      </c>
+      <c r="P61" s="28">
+        <f>O61/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="24" t="n">
+        <v>60</v>
+      </c>
+      <c r="B62" s="25" t="inlineStr">
+        <is>
+          <t>동남종합상사(주)</t>
+        </is>
+      </c>
+      <c r="C62" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D62" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E62" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F62" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G62" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H62" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="J62" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L62" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M62" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N62" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O62" s="27">
+        <f>SUM(C62:N62)</f>
+        <v/>
+      </c>
+      <c r="P62" s="28">
+        <f>O62/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="24" t="n">
         <v>61</v>
       </c>
-      <c r="D11" s="31" t="n">
-        <v>83</v>
-      </c>
-      <c r="E11" s="31" t="n">
-        <v>43</v>
-      </c>
-      <c r="F11" s="31" t="n">
-        <v>41</v>
-      </c>
-      <c r="G11" s="31" t="n">
-        <v>118</v>
-      </c>
-      <c r="H11" s="31" t="n">
-        <v>13</v>
-      </c>
-      <c r="I11" s="31" t="n">
-        <v>128</v>
-      </c>
-      <c r="J11" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K11" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L11" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M11" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N11" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O11" s="32">
-        <f>SUM(C11:N11)</f>
-        <v/>
-      </c>
-      <c r="P11" s="33">
-        <f>O11/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" s="29" t="n">
-        <v>10</v>
-      </c>
-      <c r="B12" s="30" t="inlineStr">
-        <is>
-          <t>아신상사</t>
-        </is>
-      </c>
-      <c r="C12" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="D12" s="31" t="n">
-        <v>134</v>
-      </c>
-      <c r="E12" s="31" t="n">
-        <v>152</v>
-      </c>
-      <c r="F12" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="G12" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="H12" s="31" t="n">
-        <v>138</v>
-      </c>
-      <c r="I12" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="J12" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="K12" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="L12" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="M12" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="N12" s="31" t="n">
-        <v>0</v>
-      </c>
-      <c r="O12" s="32">
-        <f>SUM(C12:N12)</f>
-        <v/>
-      </c>
-      <c r="P12" s="33">
-        <f>O12/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="34" t="n">
-        <v>11</v>
-      </c>
-      <c r="B13" s="35" t="inlineStr">
-        <is>
-          <t>유비툴</t>
-        </is>
-      </c>
-      <c r="C13" s="36" t="n">
-        <v>38</v>
-      </c>
-      <c r="D13" s="36" t="n">
-        <v>29</v>
-      </c>
-      <c r="E13" s="36" t="n">
-        <v>53</v>
-      </c>
-      <c r="F13" s="36" t="n">
-        <v>53</v>
-      </c>
-      <c r="G13" s="36" t="n">
-        <v>182</v>
-      </c>
-      <c r="H13" s="36" t="n">
-        <v>18</v>
-      </c>
-      <c r="I13" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="J13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N13" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O13" s="37">
-        <f>SUM(C13:N13)</f>
-        <v/>
-      </c>
-      <c r="P13" s="38">
-        <f>O13/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" s="34" t="n">
-        <v>12</v>
-      </c>
-      <c r="B14" s="35" t="inlineStr">
-        <is>
-          <t>알제이코리아</t>
-        </is>
-      </c>
-      <c r="C14" s="36" t="n">
+      <c r="B63" s="25" t="inlineStr">
+        <is>
+          <t>케이티툴스</t>
+        </is>
+      </c>
+      <c r="C63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G63" s="26" t="n">
+        <v>9</v>
+      </c>
+      <c r="H63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N63" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O63" s="27">
+        <f>SUM(C63:N63)</f>
+        <v/>
+      </c>
+      <c r="P63" s="28">
+        <f>O63/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="24" t="n">
+        <v>62</v>
+      </c>
+      <c r="B64" s="25" t="inlineStr">
+        <is>
+          <t>제이앤티</t>
+        </is>
+      </c>
+      <c r="C64" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D64" s="26" t="n">
+        <v>8</v>
+      </c>
+      <c r="E64" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F64" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G64" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H64" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J64" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L64" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M64" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N64" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O64" s="27">
+        <f>SUM(C64:N64)</f>
+        <v/>
+      </c>
+      <c r="P64" s="28">
+        <f>O64/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="24" t="n">
+        <v>63</v>
+      </c>
+      <c r="B65" s="25" t="inlineStr">
+        <is>
+          <t>금성툴테크</t>
+        </is>
+      </c>
+      <c r="C65" s="26" t="n">
+        <v>7</v>
+      </c>
+      <c r="D65" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E65" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F65" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G65" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H65" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J65" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L65" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M65" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N65" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O65" s="27">
+        <f>SUM(C65:N65)</f>
+        <v/>
+      </c>
+      <c r="P65" s="28">
+        <f>O65/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="24" t="n">
         <v>64</v>
       </c>
-      <c r="D14" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="36" t="n">
+      <c r="B66" s="25" t="inlineStr">
+        <is>
+          <t>대한초경공구</t>
+        </is>
+      </c>
+      <c r="C66" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D66" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="E66" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F66" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G66" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="H66" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="I66" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J66" s="26" t="n">
+        <v>1</v>
+      </c>
+      <c r="K66" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L66" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M66" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N66" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O66" s="27">
+        <f>SUM(C66:N66)</f>
+        <v/>
+      </c>
+      <c r="P66" s="28">
+        <f>O66/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="24" t="n">
+        <v>65</v>
+      </c>
+      <c r="B67" s="25" t="inlineStr">
+        <is>
+          <t>삼성패턴-코고툴(재연마)</t>
+        </is>
+      </c>
+      <c r="C67" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D67" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E67" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F67" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G67" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H67" s="26" t="n">
+        <v>6</v>
+      </c>
+      <c r="I67" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J67" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L67" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M67" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N67" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O67" s="27">
+        <f>SUM(C67:N67)</f>
+        <v/>
+      </c>
+      <c r="P67" s="28">
+        <f>O67/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="24" t="n">
+        <v>66</v>
+      </c>
+      <c r="B68" s="25" t="inlineStr">
+        <is>
+          <t>(아산)금영공구정공(주)</t>
+        </is>
+      </c>
+      <c r="C68" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D68" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E68" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F68" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G68" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H68" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="J68" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L68" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M68" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N68" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O68" s="27">
+        <f>SUM(C68:N68)</f>
+        <v/>
+      </c>
+      <c r="P68" s="28">
+        <f>O68/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="24" t="n">
+        <v>67</v>
+      </c>
+      <c r="B69" s="25" t="inlineStr">
+        <is>
+          <t>(주)툴테크신화</t>
+        </is>
+      </c>
+      <c r="C69" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D69" s="26" t="n">
+        <v>4</v>
+      </c>
+      <c r="E69" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F69" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G69" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H69" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J69" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L69" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M69" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N69" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O69" s="27">
+        <f>SUM(C69:N69)</f>
+        <v/>
+      </c>
+      <c r="P69" s="28">
+        <f>O69/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="24" t="n">
+        <v>68</v>
+      </c>
+      <c r="B70" s="25" t="inlineStr">
+        <is>
+          <t>엘엠툴스</t>
+        </is>
+      </c>
+      <c r="C70" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D70" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E70" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F70" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G70" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H70" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I70" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="J70" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L70" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M70" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N70" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O70" s="27">
+        <f>SUM(C70:N70)</f>
+        <v/>
+      </c>
+      <c r="P70" s="28">
+        <f>O70/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="24" t="n">
+        <v>69</v>
+      </c>
+      <c r="B71" s="25" t="inlineStr">
+        <is>
+          <t>유성테크</t>
+        </is>
+      </c>
+      <c r="C71" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D71" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E71" s="26" t="n">
+        <v>2</v>
+      </c>
+      <c r="F71" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G71" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H71" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="I71" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J71" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L71" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M71" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N71" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O71" s="27">
+        <f>SUM(C71:N71)</f>
+        <v/>
+      </c>
+      <c r="P71" s="28">
+        <f>O71/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="24" t="n">
         <v>70</v>
       </c>
-      <c r="F14" s="36" t="n">
-        <v>75</v>
-      </c>
-      <c r="G14" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="H14" s="36" t="n">
-        <v>58</v>
-      </c>
-      <c r="I14" s="36" t="n">
-        <v>35</v>
-      </c>
-      <c r="J14" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K14" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L14" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M14" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N14" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O14" s="37">
-        <f>SUM(C14:N14)</f>
-        <v/>
-      </c>
-      <c r="P14" s="38">
-        <f>O14/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="34" t="n">
-        <v>13</v>
-      </c>
-      <c r="B15" s="35" t="inlineStr">
-        <is>
-          <t>왕삼아공구</t>
-        </is>
-      </c>
-      <c r="C15" s="36" t="n">
-        <v>13</v>
-      </c>
-      <c r="D15" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="E15" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F15" s="36" t="n">
-        <v>40</v>
-      </c>
-      <c r="G15" s="36" t="n">
-        <v>156</v>
-      </c>
-      <c r="H15" s="36" t="n">
-        <v>54</v>
-      </c>
-      <c r="I15" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="J15" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K15" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L15" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M15" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N15" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O15" s="37">
-        <f>SUM(C15:N15)</f>
-        <v/>
-      </c>
-      <c r="P15" s="38">
-        <f>O15/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" s="34" t="n">
-        <v>14</v>
-      </c>
-      <c r="B16" s="35" t="inlineStr">
-        <is>
-          <t>(주)공화공구</t>
-        </is>
-      </c>
-      <c r="C16" s="36" t="n">
-        <v>66</v>
-      </c>
-      <c r="D16" s="36" t="n">
-        <v>47</v>
-      </c>
-      <c r="E16" s="36" t="n">
-        <v>11</v>
-      </c>
-      <c r="F16" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="G16" s="36" t="n">
-        <v>34</v>
-      </c>
-      <c r="H16" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="I16" s="36" t="n">
-        <v>90</v>
-      </c>
-      <c r="J16" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K16" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L16" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M16" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N16" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O16" s="37">
-        <f>SUM(C16:N16)</f>
-        <v/>
-      </c>
-      <c r="P16" s="38">
-        <f>O16/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="34" t="n">
-        <v>15</v>
-      </c>
-      <c r="B17" s="35" t="inlineStr">
-        <is>
-          <t>신우툴링(남동)</t>
-        </is>
-      </c>
-      <c r="C17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E17" s="36" t="n">
-        <v>32</v>
-      </c>
-      <c r="F17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G17" s="36" t="n">
-        <v>190</v>
-      </c>
-      <c r="H17" s="36" t="n">
-        <v>36</v>
-      </c>
-      <c r="I17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N17" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O17" s="37">
-        <f>SUM(C17:N17)</f>
-        <v/>
-      </c>
-      <c r="P17" s="38">
-        <f>O17/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="34" t="n">
-        <v>16</v>
-      </c>
-      <c r="B18" s="35" t="inlineStr">
-        <is>
-          <t>대륙기계공구</t>
-        </is>
-      </c>
-      <c r="C18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E18" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="F18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G18" s="36" t="n">
-        <v>60</v>
-      </c>
-      <c r="H18" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="I18" s="36" t="n">
-        <v>158</v>
-      </c>
-      <c r="J18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N18" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O18" s="37">
-        <f>SUM(C18:N18)</f>
-        <v/>
-      </c>
-      <c r="P18" s="38">
-        <f>O18/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="34" t="n">
-        <v>17</v>
-      </c>
-      <c r="B19" s="35" t="inlineStr">
-        <is>
-          <t>반석공구</t>
-        </is>
-      </c>
-      <c r="C19" s="36" t="n">
-        <v>32</v>
-      </c>
-      <c r="D19" s="36" t="n">
-        <v>22</v>
-      </c>
-      <c r="E19" s="36" t="n">
-        <v>28</v>
-      </c>
-      <c r="F19" s="36" t="n">
-        <v>13</v>
-      </c>
-      <c r="G19" s="36" t="n">
-        <v>85</v>
-      </c>
-      <c r="H19" s="36" t="n">
-        <v>56</v>
-      </c>
-      <c r="I19" s="36" t="n">
-        <v>12</v>
-      </c>
-      <c r="J19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N19" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O19" s="37">
-        <f>SUM(C19:N19)</f>
-        <v/>
-      </c>
-      <c r="P19" s="38">
-        <f>O19/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="34" t="n">
-        <v>18</v>
-      </c>
-      <c r="B20" s="35" t="inlineStr">
-        <is>
-          <t>(주)금형티에스</t>
-        </is>
-      </c>
-      <c r="C20" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="D20" s="36" t="n">
-        <v>6</v>
-      </c>
-      <c r="E20" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F20" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="G20" s="36" t="n">
-        <v>145</v>
-      </c>
-      <c r="H20" s="36" t="n">
-        <v>74</v>
-      </c>
-      <c r="I20" s="36" t="n">
-        <v>9</v>
-      </c>
-      <c r="J20" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K20" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L20" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M20" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N20" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O20" s="37">
-        <f>SUM(C20:N20)</f>
-        <v/>
-      </c>
-      <c r="P20" s="38">
-        <f>O20/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="34" t="n">
-        <v>19</v>
-      </c>
-      <c r="B21" s="35" t="inlineStr">
-        <is>
-          <t>(주)세종종합상사(미산동)</t>
-        </is>
-      </c>
-      <c r="C21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G21" s="36" t="n">
-        <v>64</v>
-      </c>
-      <c r="H21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="36" t="n">
-        <v>134</v>
-      </c>
-      <c r="J21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N21" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O21" s="37">
-        <f>SUM(C21:N21)</f>
-        <v/>
-      </c>
-      <c r="P21" s="38">
-        <f>O21/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="34" t="n">
-        <v>20</v>
-      </c>
-      <c r="B22" s="35" t="inlineStr">
-        <is>
-          <t>케이엠툴링</t>
-        </is>
-      </c>
-      <c r="C22" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="D22" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E22" s="36" t="n">
-        <v>25</v>
-      </c>
-      <c r="F22" s="36" t="n">
-        <v>40</v>
-      </c>
-      <c r="G22" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="H22" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="36" t="n">
-        <v>81</v>
-      </c>
-      <c r="J22" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K22" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L22" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M22" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N22" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O22" s="37">
-        <f>SUM(C22:N22)</f>
-        <v/>
-      </c>
-      <c r="P22" s="38">
-        <f>O22/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="34" t="n">
-        <v>21</v>
-      </c>
-      <c r="B23" s="35" t="inlineStr">
-        <is>
-          <t>서림툴링</t>
-        </is>
-      </c>
-      <c r="C23" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="D23" s="36" t="n">
-        <v>42</v>
-      </c>
-      <c r="E23" s="36" t="n">
-        <v>20</v>
-      </c>
-      <c r="F23" s="36" t="n">
-        <v>36</v>
-      </c>
-      <c r="G23" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H23" s="36" t="n">
-        <v>27</v>
-      </c>
-      <c r="I23" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="J23" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K23" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L23" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M23" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N23" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O23" s="37">
-        <f>SUM(C23:N23)</f>
-        <v/>
-      </c>
-      <c r="P23" s="38">
-        <f>O23/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" s="34" t="n">
-        <v>22</v>
-      </c>
-      <c r="B24" s="35" t="inlineStr">
-        <is>
-          <t>핫몰드엔지니어링주식회사-코고툴(재연마)</t>
-        </is>
-      </c>
-      <c r="C24" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D24" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E24" s="36" t="n">
-        <v>79</v>
-      </c>
-      <c r="F24" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G24" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H24" s="36" t="n">
-        <v>52</v>
-      </c>
-      <c r="I24" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J24" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K24" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L24" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M24" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N24" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O24" s="37">
-        <f>SUM(C24:N24)</f>
-        <v/>
-      </c>
-      <c r="P24" s="38">
-        <f>O24/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="34" t="n">
-        <v>23</v>
-      </c>
-      <c r="B25" s="35" t="inlineStr">
-        <is>
-          <t>이엠티(EMT)</t>
-        </is>
-      </c>
-      <c r="C25" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D25" s="36" t="n">
-        <v>9</v>
-      </c>
-      <c r="E25" s="36" t="n">
-        <v>104</v>
-      </c>
-      <c r="F25" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="G25" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="H25" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="I25" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J25" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K25" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L25" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M25" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N25" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O25" s="37">
-        <f>SUM(C25:N25)</f>
-        <v/>
-      </c>
-      <c r="P25" s="38">
-        <f>O25/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" s="34" t="n">
-        <v>24</v>
-      </c>
-      <c r="B26" s="35" t="inlineStr">
-        <is>
-          <t>대우툴링</t>
-        </is>
-      </c>
-      <c r="C26" s="36" t="n">
-        <v>60</v>
-      </c>
-      <c r="D26" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E26" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="F26" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G26" s="36" t="n">
-        <v>24</v>
-      </c>
-      <c r="H26" s="36" t="n">
-        <v>20</v>
-      </c>
-      <c r="I26" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="J26" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K26" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L26" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M26" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N26" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O26" s="37">
-        <f>SUM(C26:N26)</f>
-        <v/>
-      </c>
-      <c r="P26" s="38">
-        <f>O26/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" s="34" t="n">
-        <v>25</v>
-      </c>
-      <c r="B27" s="35" t="inlineStr">
-        <is>
-          <t>영창툴링</t>
-        </is>
-      </c>
-      <c r="C27" s="36" t="n">
-        <v>40</v>
-      </c>
-      <c r="D27" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="E27" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="F27" s="36" t="n">
-        <v>16</v>
-      </c>
-      <c r="G27" s="36" t="n">
-        <v>26</v>
-      </c>
-      <c r="H27" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="I27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N27" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O27" s="37">
-        <f>SUM(C27:N27)</f>
-        <v/>
-      </c>
-      <c r="P27" s="38">
-        <f>O27/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="34" t="n">
-        <v>26</v>
-      </c>
-      <c r="B28" s="35" t="inlineStr">
-        <is>
-          <t>다영툴링</t>
-        </is>
-      </c>
-      <c r="C28" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D28" s="36" t="n">
-        <v>82</v>
-      </c>
-      <c r="E28" s="36" t="n">
-        <v>17</v>
-      </c>
-      <c r="F28" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G28" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H28" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J28" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K28" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L28" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M28" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N28" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O28" s="37">
-        <f>SUM(C28:N28)</f>
-        <v/>
-      </c>
-      <c r="P28" s="38">
-        <f>O28/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" s="34" t="n">
-        <v>27</v>
-      </c>
-      <c r="B29" s="35" t="inlineStr">
-        <is>
-          <t>스마트툴스</t>
-        </is>
-      </c>
-      <c r="C29" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D29" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E29" s="36" t="n">
-        <v>95</v>
-      </c>
-      <c r="F29" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G29" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H29" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J29" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K29" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L29" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M29" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N29" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O29" s="37">
-        <f>SUM(C29:N29)</f>
-        <v/>
-      </c>
-      <c r="P29" s="38">
-        <f>O29/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" s="34" t="n">
-        <v>28</v>
-      </c>
-      <c r="B30" s="35" t="inlineStr">
-        <is>
-          <t>E-tech(이테크)</t>
-        </is>
-      </c>
-      <c r="C30" s="36" t="n">
-        <v>40</v>
-      </c>
-      <c r="D30" s="36" t="n">
-        <v>44</v>
-      </c>
-      <c r="E30" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F30" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G30" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H30" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="J30" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K30" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L30" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M30" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N30" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O30" s="37">
-        <f>SUM(C30:N30)</f>
-        <v/>
-      </c>
-      <c r="P30" s="38">
-        <f>O30/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="34" t="n">
-        <v>29</v>
-      </c>
-      <c r="B31" s="35" t="inlineStr">
-        <is>
-          <t>유성상공사</t>
-        </is>
-      </c>
-      <c r="C31" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="D31" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E31" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="F31" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="G31" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H31" s="36" t="n">
-        <v>73</v>
-      </c>
-      <c r="I31" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="J31" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K31" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L31" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M31" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N31" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O31" s="37">
-        <f>SUM(C31:N31)</f>
-        <v/>
-      </c>
-      <c r="P31" s="38">
-        <f>O31/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" s="34" t="n">
-        <v>30</v>
-      </c>
-      <c r="B32" s="35" t="inlineStr">
-        <is>
-          <t>동명ENG-코고툴(재연마)</t>
-        </is>
-      </c>
-      <c r="C32" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D32" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E32" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F32" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G32" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H32" s="36" t="n">
-        <v>84</v>
-      </c>
-      <c r="I32" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J32" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K32" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L32" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M32" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N32" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O32" s="37">
-        <f>SUM(C32:N32)</f>
-        <v/>
-      </c>
-      <c r="P32" s="38">
-        <f>O32/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" s="34" t="n">
-        <v>31</v>
-      </c>
-      <c r="B33" s="35" t="inlineStr">
-        <is>
-          <t>뉴툴(New tool)</t>
-        </is>
-      </c>
-      <c r="C33" s="36" t="n">
-        <v>70</v>
-      </c>
-      <c r="D33" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E33" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F33" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G33" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H33" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J33" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K33" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L33" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M33" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N33" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O33" s="37">
-        <f>SUM(C33:N33)</f>
-        <v/>
-      </c>
-      <c r="P33" s="38">
-        <f>O33/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="34" t="n">
-        <v>32</v>
-      </c>
-      <c r="B34" s="35" t="inlineStr">
-        <is>
-          <t>(주)정원테크</t>
-        </is>
-      </c>
-      <c r="C34" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D34" s="36" t="n">
-        <v>50</v>
-      </c>
-      <c r="E34" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F34" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G34" s="36" t="n">
-        <v>20</v>
-      </c>
-      <c r="H34" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J34" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K34" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L34" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M34" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N34" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O34" s="37">
-        <f>SUM(C34:N34)</f>
-        <v/>
-      </c>
-      <c r="P34" s="38">
-        <f>O34/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" s="34" t="n">
-        <v>33</v>
-      </c>
-      <c r="B35" s="35" t="inlineStr">
-        <is>
-          <t>광진테크</t>
-        </is>
-      </c>
-      <c r="C35" s="36" t="n">
-        <v>37</v>
-      </c>
-      <c r="D35" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E35" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="F35" s="36" t="n">
-        <v>13</v>
-      </c>
-      <c r="G35" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H35" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="I35" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J35" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K35" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L35" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M35" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N35" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O35" s="37">
-        <f>SUM(C35:N35)</f>
-        <v/>
-      </c>
-      <c r="P35" s="38">
-        <f>O35/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" s="34" t="n">
-        <v>34</v>
-      </c>
-      <c r="B36" s="35" t="inlineStr">
-        <is>
-          <t>(주)일등정밀공구(안산)</t>
-        </is>
-      </c>
-      <c r="C36" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D36" s="36" t="n">
-        <v>13</v>
-      </c>
-      <c r="E36" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F36" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G36" s="36" t="n">
-        <v>45</v>
-      </c>
-      <c r="H36" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="I36" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J36" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K36" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L36" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M36" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N36" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O36" s="37">
-        <f>SUM(C36:N36)</f>
-        <v/>
-      </c>
-      <c r="P36" s="38">
-        <f>O36/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="34" t="n">
-        <v>35</v>
-      </c>
-      <c r="B37" s="35" t="inlineStr">
-        <is>
-          <t>예일공구상사</t>
-        </is>
-      </c>
-      <c r="C37" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D37" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E37" s="36" t="n">
-        <v>57</v>
-      </c>
-      <c r="F37" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G37" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H37" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J37" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K37" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L37" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M37" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N37" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O37" s="37">
-        <f>SUM(C37:N37)</f>
-        <v/>
-      </c>
-      <c r="P37" s="38">
-        <f>O37/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" s="34" t="n">
-        <v>36</v>
-      </c>
-      <c r="B38" s="35" t="inlineStr">
-        <is>
-          <t>(주)전진공구</t>
-        </is>
-      </c>
-      <c r="C38" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D38" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E38" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F38" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G38" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H38" s="36" t="n">
-        <v>53</v>
-      </c>
-      <c r="I38" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="J38" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K38" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L38" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M38" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N38" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O38" s="37">
-        <f>SUM(C38:N38)</f>
-        <v/>
-      </c>
-      <c r="P38" s="38">
-        <f>O38/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" s="34" t="n">
-        <v>37</v>
-      </c>
-      <c r="B39" s="35" t="inlineStr">
-        <is>
-          <t>맨날툴이야</t>
-        </is>
-      </c>
-      <c r="C39" s="36" t="n">
-        <v>13</v>
-      </c>
-      <c r="D39" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E39" s="36" t="n">
-        <v>14</v>
-      </c>
-      <c r="F39" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G39" s="36" t="n">
-        <v>16</v>
-      </c>
-      <c r="H39" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="J39" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K39" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L39" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M39" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N39" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O39" s="37">
-        <f>SUM(C39:N39)</f>
-        <v/>
-      </c>
-      <c r="P39" s="38">
-        <f>O39/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="34" t="n">
-        <v>38</v>
-      </c>
-      <c r="B40" s="35" t="inlineStr">
-        <is>
-          <t>하나테크</t>
-        </is>
-      </c>
-      <c r="C40" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D40" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E40" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F40" s="36" t="n">
-        <v>39</v>
-      </c>
-      <c r="G40" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H40" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="I40" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="J40" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K40" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L40" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M40" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N40" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O40" s="37">
-        <f>SUM(C40:N40)</f>
-        <v/>
-      </c>
-      <c r="P40" s="38">
-        <f>O40/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="41">
-      <c r="A41" s="34" t="n">
-        <v>39</v>
-      </c>
-      <c r="B41" s="35" t="inlineStr">
-        <is>
-          <t>대성테크</t>
-        </is>
-      </c>
-      <c r="C41" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D41" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E41" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F41" s="36" t="n">
-        <v>29</v>
-      </c>
-      <c r="G41" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H41" s="36" t="n">
-        <v>12</v>
-      </c>
-      <c r="I41" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J41" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K41" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L41" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M41" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N41" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O41" s="37">
-        <f>SUM(C41:N41)</f>
-        <v/>
-      </c>
-      <c r="P41" s="38">
-        <f>O41/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="42">
-      <c r="A42" s="34" t="n">
-        <v>40</v>
-      </c>
-      <c r="B42" s="35" t="inlineStr">
-        <is>
-          <t>인코테크 포승</t>
-        </is>
-      </c>
-      <c r="C42" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D42" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E42" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F42" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G42" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H42" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="36" t="n">
-        <v>40</v>
-      </c>
-      <c r="J42" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K42" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L42" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M42" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N42" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O42" s="37">
-        <f>SUM(C42:N42)</f>
-        <v/>
-      </c>
-      <c r="P42" s="38">
-        <f>O42/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="34" t="n">
-        <v>41</v>
-      </c>
-      <c r="B43" s="35" t="inlineStr">
-        <is>
-          <t>대명종합공구-코고툴(재연마)</t>
-        </is>
-      </c>
-      <c r="C43" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D43" s="36" t="n">
-        <v>12</v>
-      </c>
-      <c r="E43" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F43" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="G43" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H43" s="36" t="n">
-        <v>20</v>
-      </c>
-      <c r="I43" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J43" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K43" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L43" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M43" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N43" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O43" s="37">
-        <f>SUM(C43:N43)</f>
-        <v/>
-      </c>
-      <c r="P43" s="38">
-        <f>O43/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="34" t="n">
-        <v>42</v>
-      </c>
-      <c r="B44" s="35" t="inlineStr">
-        <is>
-          <t>공구백화점(미산동)</t>
-        </is>
-      </c>
-      <c r="C44" s="36" t="n">
-        <v>16</v>
-      </c>
-      <c r="D44" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="E44" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="F44" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="G44" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H44" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="I44" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J44" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K44" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L44" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M44" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N44" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O44" s="37">
-        <f>SUM(C44:N44)</f>
-        <v/>
-      </c>
-      <c r="P44" s="38">
-        <f>O44/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="34" t="n">
-        <v>43</v>
-      </c>
-      <c r="B45" s="35" t="inlineStr">
-        <is>
-          <t>(주)바로공구(정남)</t>
-        </is>
-      </c>
-      <c r="C45" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D45" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E45" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="F45" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G45" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H45" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="36" t="n">
-        <v>21</v>
-      </c>
-      <c r="J45" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K45" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L45" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M45" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N45" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O45" s="37">
-        <f>SUM(C45:N45)</f>
-        <v/>
-      </c>
-      <c r="P45" s="38">
-        <f>O45/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="34" t="n">
-        <v>44</v>
-      </c>
-      <c r="B46" s="35" t="inlineStr">
-        <is>
-          <t>공구공구</t>
-        </is>
-      </c>
-      <c r="C46" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D46" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E46" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F46" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G46" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="H46" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J46" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K46" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L46" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M46" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N46" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O46" s="37">
-        <f>SUM(C46:N46)</f>
-        <v/>
-      </c>
-      <c r="P46" s="38">
-        <f>O46/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="34" t="n">
-        <v>45</v>
-      </c>
-      <c r="B47" s="35" t="inlineStr">
-        <is>
-          <t>(주)코리아테크닉스</t>
-        </is>
-      </c>
-      <c r="C47" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D47" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E47" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="F47" s="36" t="n">
-        <v>15</v>
-      </c>
-      <c r="G47" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H47" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J47" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K47" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L47" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M47" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N47" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O47" s="37">
-        <f>SUM(C47:N47)</f>
-        <v/>
-      </c>
-      <c r="P47" s="38">
-        <f>O47/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="34" t="n">
-        <v>46</v>
-      </c>
-      <c r="B48" s="35" t="inlineStr">
-        <is>
-          <t>지니툴(구로)_코고툴</t>
-        </is>
-      </c>
-      <c r="C48" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D48" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E48" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F48" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G48" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H48" s="36" t="n">
-        <v>30</v>
-      </c>
-      <c r="I48" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J48" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K48" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L48" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M48" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N48" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O48" s="37">
-        <f>SUM(C48:N48)</f>
-        <v/>
-      </c>
-      <c r="P48" s="38">
-        <f>O48/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="34" t="n">
-        <v>47</v>
-      </c>
-      <c r="B49" s="35" t="inlineStr">
-        <is>
-          <t>유성종합공구</t>
-        </is>
-      </c>
-      <c r="C49" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D49" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="E49" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="F49" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G49" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="H49" s="36" t="n">
-        <v>5</v>
-      </c>
-      <c r="I49" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="J49" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K49" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L49" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M49" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N49" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O49" s="37">
-        <f>SUM(C49:N49)</f>
-        <v/>
-      </c>
-      <c r="P49" s="38">
-        <f>O49/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" s="34" t="n">
-        <v>48</v>
-      </c>
-      <c r="B50" s="35" t="inlineStr">
-        <is>
-          <t>유진상사(문래)</t>
-        </is>
-      </c>
-      <c r="C50" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D50" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="E50" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F50" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G50" s="36" t="n">
-        <v>19</v>
-      </c>
-      <c r="H50" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="36" t="n">
+      <c r="B72" s="25" t="inlineStr">
+        <is>
+          <t>우주툴링</t>
+        </is>
+      </c>
+      <c r="C72" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="D72" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="E72" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="F72" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="G72" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="H72" s="26" t="n">
         <v>1</v>
       </c>
-      <c r="J50" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K50" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L50" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M50" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N50" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O50" s="37">
-        <f>SUM(C50:N50)</f>
-        <v/>
-      </c>
-      <c r="P50" s="38">
-        <f>O50/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" s="34" t="n">
-        <v>49</v>
-      </c>
-      <c r="B51" s="35" t="inlineStr">
-        <is>
-          <t>코끼리공구</t>
-        </is>
-      </c>
-      <c r="C51" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D51" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E51" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F51" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G51" s="36" t="n">
-        <v>3</v>
-      </c>
-      <c r="H51" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="36" t="n">
-        <v>13</v>
-      </c>
-      <c r="J51" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K51" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L51" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M51" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N51" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O51" s="37">
-        <f>SUM(C51:N51)</f>
-        <v/>
-      </c>
-      <c r="P51" s="38">
-        <f>O51/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" s="34" t="n">
-        <v>50</v>
-      </c>
-      <c r="B52" s="35" t="inlineStr">
-        <is>
-          <t>대양공구(인천)</t>
-        </is>
-      </c>
-      <c r="C52" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D52" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E52" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F52" s="36" t="n">
-        <v>14</v>
-      </c>
-      <c r="G52" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H52" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J52" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K52" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L52" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M52" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N52" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O52" s="37">
-        <f>SUM(C52:N52)</f>
-        <v/>
-      </c>
-      <c r="P52" s="38">
-        <f>O52/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" s="34" t="n">
-        <v>51</v>
-      </c>
-      <c r="B53" s="35" t="inlineStr">
-        <is>
-          <t>(주)두영</t>
-        </is>
-      </c>
-      <c r="C53" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D53" s="36" t="n">
-        <v>14</v>
-      </c>
-      <c r="E53" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F53" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G53" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H53" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J53" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K53" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L53" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M53" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N53" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O53" s="37">
-        <f>SUM(C53:N53)</f>
-        <v/>
-      </c>
-      <c r="P53" s="38">
-        <f>O53/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="54">
-      <c r="A54" s="34" t="n">
-        <v>52</v>
-      </c>
-      <c r="B54" s="35" t="inlineStr">
-        <is>
-          <t>N.T.S(엔티에스)-코고툴</t>
-        </is>
-      </c>
-      <c r="C54" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D54" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E54" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F54" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G54" s="36" t="n">
-        <v>12</v>
-      </c>
-      <c r="H54" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="J54" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K54" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L54" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M54" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N54" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O54" s="37">
-        <f>SUM(C54:N54)</f>
-        <v/>
-      </c>
-      <c r="P54" s="38">
-        <f>O54/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="55">
-      <c r="A55" s="34" t="n">
-        <v>53</v>
-      </c>
-      <c r="B55" s="35" t="inlineStr">
-        <is>
-          <t>(주)금천종합공구(독산)</t>
-        </is>
-      </c>
-      <c r="C55" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D55" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E55" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="F55" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G55" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="H55" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J55" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K55" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L55" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M55" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N55" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O55" s="37">
-        <f>SUM(C55:N55)</f>
-        <v/>
-      </c>
-      <c r="P55" s="38">
-        <f>O55/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="56">
-      <c r="A56" s="34" t="n">
-        <v>54</v>
-      </c>
-      <c r="B56" s="35" t="inlineStr">
-        <is>
-          <t>신우툴스</t>
-        </is>
-      </c>
-      <c r="C56" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D56" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E56" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F56" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G56" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H56" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="36" t="n">
-        <v>12</v>
-      </c>
-      <c r="J56" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K56" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L56" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M56" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N56" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O56" s="37">
-        <f>SUM(C56:N56)</f>
-        <v/>
-      </c>
-      <c r="P56" s="38">
-        <f>O56/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="57">
-      <c r="A57" s="34" t="n">
-        <v>55</v>
-      </c>
-      <c r="B57" s="35" t="inlineStr">
-        <is>
-          <t>세운상사</t>
-        </is>
-      </c>
-      <c r="C57" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D57" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E57" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F57" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="G57" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H57" s="36" t="n">
-        <v>11</v>
-      </c>
-      <c r="I57" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J57" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K57" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L57" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M57" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N57" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O57" s="37">
-        <f>SUM(C57:N57)</f>
-        <v/>
-      </c>
-      <c r="P57" s="38">
-        <f>O57/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="58">
-      <c r="A58" s="34" t="n">
-        <v>56</v>
-      </c>
-      <c r="B58" s="35" t="inlineStr">
-        <is>
-          <t>웰크리에이트-코고툴(재연마)</t>
-        </is>
-      </c>
-      <c r="C58" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D58" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E58" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F58" s="36" t="n">
-        <v>10</v>
-      </c>
-      <c r="G58" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H58" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J58" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K58" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L58" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M58" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N58" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O58" s="37">
-        <f>SUM(C58:N58)</f>
-        <v/>
-      </c>
-      <c r="P58" s="38">
-        <f>O58/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="59">
-      <c r="A59" s="34" t="n">
-        <v>57</v>
-      </c>
-      <c r="B59" s="35" t="inlineStr">
-        <is>
-          <t>케이티툴스</t>
-        </is>
-      </c>
-      <c r="C59" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D59" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E59" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F59" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G59" s="36" t="n">
-        <v>9</v>
-      </c>
-      <c r="H59" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J59" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K59" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L59" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M59" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N59" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O59" s="37">
-        <f>SUM(C59:N59)</f>
-        <v/>
-      </c>
-      <c r="P59" s="38">
-        <f>O59/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="60">
-      <c r="A60" s="34" t="n">
-        <v>58</v>
-      </c>
-      <c r="B60" s="35" t="inlineStr">
-        <is>
-          <t>동남종합상사(주)</t>
-        </is>
-      </c>
-      <c r="C60" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D60" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E60" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F60" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G60" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H60" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="36" t="n">
-        <v>9</v>
-      </c>
-      <c r="J60" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K60" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L60" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M60" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N60" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O60" s="37">
-        <f>SUM(C60:N60)</f>
-        <v/>
-      </c>
-      <c r="P60" s="38">
-        <f>O60/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="61">
-      <c r="A61" s="34" t="n">
-        <v>59</v>
-      </c>
-      <c r="B61" s="35" t="inlineStr">
-        <is>
-          <t>영호종합공구(향남)</t>
-        </is>
-      </c>
-      <c r="C61" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D61" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E61" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F61" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G61" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H61" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="I61" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J61" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K61" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L61" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M61" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N61" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O61" s="37">
-        <f>SUM(C61:N61)</f>
-        <v/>
-      </c>
-      <c r="P61" s="38">
-        <f>O61/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="62">
-      <c r="A62" s="34" t="n">
-        <v>60</v>
-      </c>
-      <c r="B62" s="35" t="inlineStr">
-        <is>
-          <t>제이앤티</t>
-        </is>
-      </c>
-      <c r="C62" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D62" s="36" t="n">
-        <v>8</v>
-      </c>
-      <c r="E62" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F62" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G62" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H62" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J62" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K62" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L62" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M62" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N62" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O62" s="37">
-        <f>SUM(C62:N62)</f>
-        <v/>
-      </c>
-      <c r="P62" s="38">
-        <f>O62/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="34" t="n">
-        <v>61</v>
-      </c>
-      <c r="B63" s="35" t="inlineStr">
-        <is>
-          <t>금성툴테크</t>
-        </is>
-      </c>
-      <c r="C63" s="36" t="n">
-        <v>7</v>
-      </c>
-      <c r="D63" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E63" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F63" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G63" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H63" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J63" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K63" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L63" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M63" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N63" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O63" s="37">
-        <f>SUM(C63:N63)</f>
-        <v/>
-      </c>
-      <c r="P63" s="38">
-        <f>O63/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="34" t="n">
-        <v>62</v>
-      </c>
-      <c r="B64" s="35" t="inlineStr">
-        <is>
-          <t>대한초경공구</t>
-        </is>
-      </c>
-      <c r="C64" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D64" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="E64" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F64" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G64" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="H64" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="I64" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="J64" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K64" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L64" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M64" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N64" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O64" s="37">
-        <f>SUM(C64:N64)</f>
-        <v/>
-      </c>
-      <c r="P64" s="38">
-        <f>O64/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" s="34" t="n">
-        <v>63</v>
-      </c>
-      <c r="B65" s="35" t="inlineStr">
-        <is>
-          <t>삼성패턴-코고툴(재연마)</t>
-        </is>
-      </c>
-      <c r="C65" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D65" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E65" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F65" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G65" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H65" s="36" t="n">
-        <v>6</v>
-      </c>
-      <c r="I65" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J65" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K65" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L65" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M65" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N65" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O65" s="37">
-        <f>SUM(C65:N65)</f>
-        <v/>
-      </c>
-      <c r="P65" s="38">
-        <f>O65/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" s="34" t="n">
-        <v>64</v>
-      </c>
-      <c r="B66" s="35" t="inlineStr">
-        <is>
-          <t>(주)성환공구</t>
-        </is>
-      </c>
-      <c r="C66" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="D66" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E66" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="F66" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="G66" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H66" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J66" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K66" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L66" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M66" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N66" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O66" s="37">
-        <f>SUM(C66:N66)</f>
-        <v/>
-      </c>
-      <c r="P66" s="38">
-        <f>O66/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" s="34" t="n">
-        <v>65</v>
-      </c>
-      <c r="B67" s="35" t="inlineStr">
-        <is>
-          <t>(주)툴테크신화</t>
-        </is>
-      </c>
-      <c r="C67" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D67" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="E67" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F67" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G67" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H67" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J67" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K67" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L67" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M67" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N67" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O67" s="37">
-        <f>SUM(C67:N67)</f>
-        <v/>
-      </c>
-      <c r="P67" s="38">
-        <f>O67/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" s="34" t="n">
-        <v>66</v>
-      </c>
-      <c r="B68" s="35" t="inlineStr">
-        <is>
-          <t>(아산)금영공구정공(주)</t>
-        </is>
-      </c>
-      <c r="C68" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D68" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E68" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F68" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G68" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H68" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="36" t="n">
-        <v>4</v>
-      </c>
-      <c r="J68" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K68" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L68" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M68" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N68" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O68" s="37">
-        <f>SUM(C68:N68)</f>
-        <v/>
-      </c>
-      <c r="P68" s="38">
-        <f>O68/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" s="34" t="n">
-        <v>67</v>
-      </c>
-      <c r="B69" s="35" t="inlineStr">
-        <is>
-          <t>유성테크</t>
-        </is>
-      </c>
-      <c r="C69" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D69" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E69" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="F69" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G69" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H69" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J69" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K69" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L69" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M69" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N69" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O69" s="37">
-        <f>SUM(C69:N69)</f>
-        <v/>
-      </c>
-      <c r="P69" s="38">
-        <f>O69/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" s="34" t="n">
-        <v>68</v>
-      </c>
-      <c r="B70" s="35" t="inlineStr">
-        <is>
-          <t>엘엠툴스</t>
-        </is>
-      </c>
-      <c r="C70" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D70" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E70" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F70" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G70" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H70" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="36" t="n">
-        <v>2</v>
-      </c>
-      <c r="J70" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K70" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L70" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M70" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N70" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O70" s="37">
-        <f>SUM(C70:N70)</f>
-        <v/>
-      </c>
-      <c r="P70" s="38">
-        <f>O70/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="71">
-      <c r="A71" s="34" t="n">
-        <v>69</v>
-      </c>
-      <c r="B71" s="35" t="inlineStr">
-        <is>
-          <t>우주툴링</t>
-        </is>
-      </c>
-      <c r="C71" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D71" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E71" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="F71" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="G71" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="H71" s="36" t="n">
-        <v>1</v>
-      </c>
-      <c r="I71" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="J71" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="K71" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="L71" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="M71" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="N71" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="O71" s="37">
-        <f>SUM(C71:N71)</f>
-        <v/>
-      </c>
-      <c r="P71" s="38">
-        <f>O71/O$72</f>
-        <v/>
-      </c>
-    </row>
-    <row r="72">
-      <c r="A72" s="39" t="inlineStr">
+      <c r="I72" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="J72" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="K72" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="L72" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="M72" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="N72" s="26" t="n">
+        <v>0</v>
+      </c>
+      <c r="O72" s="27">
+        <f>SUM(C72:N72)</f>
+        <v/>
+      </c>
+      <c r="P72" s="28">
+        <f>O72/O$73</f>
+        <v/>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="39" t="inlineStr">
         <is>
           <t>합계</t>
         </is>
       </c>
-      <c r="B72" s="39" t="n"/>
-      <c r="C72" s="40">
-        <f>SUM(C3:C71)</f>
-        <v/>
-      </c>
-      <c r="D72" s="40">
-        <f>SUM(D3:D71)</f>
-        <v/>
-      </c>
-      <c r="E72" s="40">
-        <f>SUM(E3:E71)</f>
-        <v/>
-      </c>
-      <c r="F72" s="40">
-        <f>SUM(F3:F71)</f>
-        <v/>
-      </c>
-      <c r="G72" s="40">
-        <f>SUM(G3:G71)</f>
-        <v/>
-      </c>
-      <c r="H72" s="40">
-        <f>SUM(H3:H71)</f>
-        <v/>
-      </c>
-      <c r="I72" s="40">
-        <f>SUM(I3:I71)</f>
-        <v/>
-      </c>
-      <c r="J72" s="40">
-        <f>SUM(J3:J71)</f>
-        <v/>
-      </c>
-      <c r="K72" s="40">
-        <f>SUM(K3:K71)</f>
-        <v/>
-      </c>
-      <c r="L72" s="40">
-        <f>SUM(L3:L71)</f>
-        <v/>
-      </c>
-      <c r="M72" s="40">
-        <f>SUM(M3:M71)</f>
-        <v/>
-      </c>
-      <c r="N72" s="40">
-        <f>SUM(N3:N71)</f>
-        <v/>
-      </c>
-      <c r="O72" s="40">
-        <f>SUM(O3:O71)</f>
-        <v/>
-      </c>
-      <c r="P72" s="41" t="n">
+      <c r="B73" s="43" t="n"/>
+      <c r="C73" s="40">
+        <f>SUM(C3:C72)</f>
+        <v/>
+      </c>
+      <c r="D73" s="40">
+        <f>SUM(D3:D72)</f>
+        <v/>
+      </c>
+      <c r="E73" s="40">
+        <f>SUM(E3:E72)</f>
+        <v/>
+      </c>
+      <c r="F73" s="40">
+        <f>SUM(F3:F72)</f>
+        <v/>
+      </c>
+      <c r="G73" s="40">
+        <f>SUM(G3:G72)</f>
+        <v/>
+      </c>
+      <c r="H73" s="40">
+        <f>SUM(H3:H72)</f>
+        <v/>
+      </c>
+      <c r="I73" s="40">
+        <f>SUM(I3:I72)</f>
+        <v/>
+      </c>
+      <c r="J73" s="40">
+        <f>SUM(J3:J72)</f>
+        <v/>
+      </c>
+      <c r="K73" s="40">
+        <f>SUM(K3:K72)</f>
+        <v/>
+      </c>
+      <c r="L73" s="40">
+        <f>SUM(L3:L72)</f>
+        <v/>
+      </c>
+      <c r="M73" s="40">
+        <f>SUM(M3:M72)</f>
+        <v/>
+      </c>
+      <c r="N73" s="40">
+        <f>SUM(N3:N72)</f>
+        <v/>
+      </c>
+      <c r="O73" s="40">
+        <f>SUM(O3:O72)</f>
+        <v/>
+      </c>
+      <c r="P73" s="41" t="n">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:P1"/>
-    <mergeCell ref="A72:B72"/>
+    <mergeCell ref="A73:B73"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4924,7 +5000,7 @@
         <v/>
       </c>
       <c r="F3" s="7" t="n">
-        <v>1471</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="4">
@@ -4972,7 +5048,7 @@
         <v/>
       </c>
       <c r="F5" s="7" t="n">
-        <v>538</v>
+        <v>578</v>
       </c>
     </row>
     <row r="6">
@@ -5020,7 +5096,7 @@
         <v/>
       </c>
       <c r="F7" s="7" t="n">
-        <v>639</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8">
@@ -5044,7 +5120,7 @@
         <v/>
       </c>
       <c r="F8" s="17" t="n">
-        <v>268</v>
+        <v>342</v>
       </c>
     </row>
     <row r="9">
@@ -5092,7 +5168,7 @@
         <v/>
       </c>
       <c r="F10" s="17" t="n">
-        <v>487</v>
+        <v>554</v>
       </c>
     </row>
     <row r="11">
@@ -5116,7 +5192,7 @@
         <v/>
       </c>
       <c r="F11" s="17" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="12">
@@ -5212,7 +5288,7 @@
         <v/>
       </c>
       <c r="F15" s="17" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="16">
@@ -5236,7 +5312,7 @@
         <v/>
       </c>
       <c r="F16" s="17" t="n">
-        <v>248</v>
+        <v>307</v>
       </c>
     </row>
     <row r="17">
@@ -5284,7 +5360,7 @@
         <v/>
       </c>
       <c r="F18" s="17" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
     </row>
     <row r="19">
@@ -5308,7 +5384,7 @@
         <v/>
       </c>
       <c r="F19" s="17" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20">
@@ -5332,7 +5408,7 @@
         <v/>
       </c>
       <c r="F20" s="17" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21">
@@ -5356,7 +5432,7 @@
         <v/>
       </c>
       <c r="F21" s="17" t="n">
-        <v>937</v>
+        <v>953</v>
       </c>
     </row>
     <row r="22">
@@ -5404,7 +5480,7 @@
         <v/>
       </c>
       <c r="F23" s="17" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
     </row>
     <row r="24">
@@ -5428,7 +5504,7 @@
         <v/>
       </c>
       <c r="F24" s="17" t="n">
-        <v>603</v>
+        <v>626</v>
       </c>
     </row>
     <row r="25">
@@ -5452,7 +5528,7 @@
         <v/>
       </c>
       <c r="F25" s="17" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="26">
@@ -5500,7 +5576,7 @@
         <v/>
       </c>
       <c r="F27" s="17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28">
@@ -5609,7 +5685,7 @@
         <v/>
       </c>
       <c r="F3" s="7" t="n">
-        <v>1427</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="4">
@@ -5633,7 +5709,7 @@
         <v/>
       </c>
       <c r="F4" s="7" t="n">
-        <v>1336</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="5">
@@ -5657,7 +5733,7 @@
         <v/>
       </c>
       <c r="F5" s="7" t="n">
-        <v>937</v>
+        <v>953</v>
       </c>
     </row>
     <row r="6">
@@ -5681,7 +5757,7 @@
         <v/>
       </c>
       <c r="F6" s="7" t="n">
-        <v>424</v>
+        <v>579</v>
       </c>
     </row>
     <row r="7">
@@ -5705,7 +5781,7 @@
         <v/>
       </c>
       <c r="F7" s="7" t="n">
-        <v>639</v>
+        <v>746</v>
       </c>
     </row>
     <row r="8">
@@ -5729,7 +5805,7 @@
         <v/>
       </c>
       <c r="F8" s="17" t="n">
-        <v>603</v>
+        <v>626</v>
       </c>
     </row>
     <row r="9">
@@ -5753,7 +5829,7 @@
         <v/>
       </c>
       <c r="F9" s="17" t="n">
-        <v>487</v>
+        <v>554</v>
       </c>
     </row>
     <row r="10">
@@ -5801,7 +5877,7 @@
         <v/>
       </c>
       <c r="F11" s="17" t="n">
-        <v>538</v>
+        <v>578</v>
       </c>
     </row>
     <row r="12">
@@ -5825,7 +5901,7 @@
         <v/>
       </c>
       <c r="F12" s="17" t="n">
-        <v>1471</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="13">
@@ -5849,7 +5925,7 @@
         <v/>
       </c>
       <c r="F13" s="17" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="14">
@@ -5873,7 +5949,7 @@
         <v/>
       </c>
       <c r="F14" s="17" t="n">
-        <v>268</v>
+        <v>342</v>
       </c>
     </row>
     <row r="15">
@@ -5921,7 +5997,7 @@
         <v/>
       </c>
       <c r="F16" s="17" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
     </row>
     <row r="17">
@@ -5969,7 +6045,7 @@
         <v/>
       </c>
       <c r="F18" s="17" t="n">
-        <v>248</v>
+        <v>307</v>
       </c>
     </row>
     <row r="19">
@@ -5993,7 +6069,7 @@
         <v/>
       </c>
       <c r="F19" s="17" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="20">
@@ -6041,7 +6117,7 @@
         <v/>
       </c>
       <c r="F21" s="17" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="22">
@@ -6161,7 +6237,7 @@
         <v/>
       </c>
       <c r="F26" s="17" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="27">
@@ -6281,7 +6357,7 @@
         <v/>
       </c>
       <c r="F31" s="17" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32">
@@ -6305,7 +6381,7 @@
         <v/>
       </c>
       <c r="F32" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="33">
@@ -6414,7 +6490,7 @@
         <v/>
       </c>
       <c r="F3" s="7" t="n">
-        <v>937</v>
+        <v>953</v>
       </c>
     </row>
     <row r="4">
@@ -6438,7 +6514,7 @@
         <v/>
       </c>
       <c r="F4" s="7" t="n">
-        <v>424</v>
+        <v>579</v>
       </c>
     </row>
     <row r="5">
@@ -6462,7 +6538,7 @@
         <v/>
       </c>
       <c r="F5" s="7" t="n">
-        <v>1336</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="6">
@@ -6486,7 +6562,7 @@
         <v/>
       </c>
       <c r="F6" s="7" t="n">
-        <v>1427</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="7">
@@ -6510,7 +6586,7 @@
         <v/>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1471</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="8">
@@ -6582,7 +6658,7 @@
         <v/>
       </c>
       <c r="F10" s="17" t="n">
-        <v>131</v>
+        <v>188</v>
       </c>
     </row>
     <row r="11">
@@ -6606,7 +6682,7 @@
         <v/>
       </c>
       <c r="F11" s="17" t="n">
-        <v>639</v>
+        <v>746</v>
       </c>
     </row>
     <row r="12">
@@ -6702,7 +6778,7 @@
         <v/>
       </c>
       <c r="F15" s="17" t="n">
-        <v>487</v>
+        <v>554</v>
       </c>
     </row>
     <row r="16">
@@ -6726,7 +6802,7 @@
         <v/>
       </c>
       <c r="F16" s="17" t="n">
-        <v>538</v>
+        <v>578</v>
       </c>
     </row>
     <row r="17">
@@ -6750,7 +6826,7 @@
         <v/>
       </c>
       <c r="F17" s="17" t="n">
-        <v>258</v>
+        <v>325</v>
       </c>
     </row>
     <row r="18">
@@ -6774,7 +6850,7 @@
         <v/>
       </c>
       <c r="F18" s="17" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="19">
@@ -6798,7 +6874,7 @@
         <v/>
       </c>
       <c r="F19" s="17" t="n">
-        <v>248</v>
+        <v>307</v>
       </c>
     </row>
     <row r="20">
@@ -6846,7 +6922,7 @@
         <v/>
       </c>
       <c r="F21" s="17" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22">
@@ -6942,7 +7018,7 @@
         <v/>
       </c>
       <c r="F25" s="17" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26">
@@ -6966,7 +7042,7 @@
         <v/>
       </c>
       <c r="F26" s="17" t="n">
-        <v>268</v>
+        <v>342</v>
       </c>
     </row>
     <row r="27">
@@ -6990,7 +7066,7 @@
         <v/>
       </c>
       <c r="F27" s="17" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="28">
@@ -7014,7 +7090,7 @@
         <v/>
       </c>
       <c r="F28" s="17" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="29">
@@ -7062,7 +7138,7 @@
         <v/>
       </c>
       <c r="F30" s="17" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="31">
@@ -7086,7 +7162,7 @@
         <v/>
       </c>
       <c r="F31" s="17" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="32">
@@ -7110,7 +7186,7 @@
         <v/>
       </c>
       <c r="F32" s="17" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33">
@@ -7158,7 +7234,7 @@
         <v/>
       </c>
       <c r="F34" s="17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="35">
@@ -7315,7 +7391,7 @@
         <v/>
       </c>
       <c r="F4" s="7" t="n">
-        <v>1336</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="5">
@@ -7339,7 +7415,7 @@
         <v/>
       </c>
       <c r="F5" s="7" t="n">
-        <v>1427</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="6">
@@ -7363,7 +7439,7 @@
         <v/>
       </c>
       <c r="F6" s="7" t="n">
-        <v>937</v>
+        <v>953</v>
       </c>
     </row>
     <row r="7">
@@ -7387,7 +7463,7 @@
         <v/>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1471</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="8">
@@ -7411,7 +7487,7 @@
         <v/>
       </c>
       <c r="F8" s="17" t="n">
-        <v>639</v>
+        <v>746</v>
       </c>
     </row>
     <row r="9">
@@ -7459,7 +7535,7 @@
         <v/>
       </c>
       <c r="F10" s="17" t="n">
-        <v>603</v>
+        <v>626</v>
       </c>
     </row>
     <row r="11">
@@ -7507,7 +7583,7 @@
         <v/>
       </c>
       <c r="F12" s="17" t="n">
-        <v>487</v>
+        <v>554</v>
       </c>
     </row>
     <row r="13">
@@ -7531,7 +7607,7 @@
         <v/>
       </c>
       <c r="F13" s="17" t="n">
-        <v>538</v>
+        <v>578</v>
       </c>
     </row>
     <row r="14">
@@ -7555,7 +7631,7 @@
         <v/>
       </c>
       <c r="F14" s="17" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="15">
@@ -7627,7 +7703,7 @@
         <v/>
       </c>
       <c r="F17" s="17" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18">
@@ -7723,7 +7799,7 @@
         <v/>
       </c>
       <c r="F21" s="17" t="n">
-        <v>14</v>
+        <v>18</v>
       </c>
     </row>
     <row r="22">
@@ -7747,7 +7823,7 @@
         <v/>
       </c>
       <c r="F22" s="17" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="23">
@@ -7771,7 +7847,7 @@
         <v/>
       </c>
       <c r="F23" s="17" t="n">
-        <v>248</v>
+        <v>307</v>
       </c>
     </row>
     <row r="24">
@@ -7795,7 +7871,7 @@
         <v/>
       </c>
       <c r="F24" s="17" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="25">
@@ -7819,7 +7895,7 @@
         <v/>
       </c>
       <c r="F25" s="17" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
     </row>
     <row r="26">
@@ -7915,7 +7991,7 @@
         <v/>
       </c>
       <c r="F29" s="17" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="30">
@@ -7939,7 +8015,7 @@
         <v/>
       </c>
       <c r="F30" s="17" t="n">
-        <v>268</v>
+        <v>342</v>
       </c>
     </row>
     <row r="31">
@@ -7963,7 +8039,7 @@
         <v/>
       </c>
       <c r="F31" s="17" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
     </row>
     <row r="32">
@@ -8096,7 +8172,7 @@
         <v/>
       </c>
       <c r="F3" s="7" t="n">
-        <v>1427</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="4">
@@ -8120,7 +8196,7 @@
         <v/>
       </c>
       <c r="F4" s="7" t="n">
-        <v>603</v>
+        <v>626</v>
       </c>
     </row>
     <row r="5">
@@ -8144,7 +8220,7 @@
         <v/>
       </c>
       <c r="F5" s="7" t="n">
-        <v>258</v>
+        <v>325</v>
       </c>
     </row>
     <row r="6">
@@ -8192,7 +8268,7 @@
         <v/>
       </c>
       <c r="F7" s="7" t="n">
-        <v>1336</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="8">
@@ -8216,7 +8292,7 @@
         <v/>
       </c>
       <c r="F8" s="17" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="9">
@@ -8264,7 +8340,7 @@
         <v/>
       </c>
       <c r="F10" s="17" t="n">
-        <v>487</v>
+        <v>554</v>
       </c>
     </row>
     <row r="11">
@@ -8288,7 +8364,7 @@
         <v/>
       </c>
       <c r="F11" s="17" t="n">
-        <v>937</v>
+        <v>953</v>
       </c>
     </row>
     <row r="12">
@@ -8312,7 +8388,7 @@
         <v/>
       </c>
       <c r="F12" s="17" t="n">
-        <v>248</v>
+        <v>307</v>
       </c>
     </row>
     <row r="13">
@@ -8336,7 +8412,7 @@
         <v/>
       </c>
       <c r="F13" s="17" t="n">
-        <v>1471</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="14">
@@ -8360,7 +8436,7 @@
         <v/>
       </c>
       <c r="F14" s="17" t="n">
-        <v>538</v>
+        <v>578</v>
       </c>
     </row>
     <row r="15">
@@ -8408,7 +8484,7 @@
         <v/>
       </c>
       <c r="F16" s="17" t="n">
-        <v>639</v>
+        <v>746</v>
       </c>
     </row>
     <row r="17">
@@ -8432,7 +8508,7 @@
         <v/>
       </c>
       <c r="F17" s="17" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="18">
@@ -8456,7 +8532,7 @@
         <v/>
       </c>
       <c r="F18" s="17" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="19">
@@ -8480,7 +8556,7 @@
         <v/>
       </c>
       <c r="F19" s="17" t="n">
-        <v>268</v>
+        <v>342</v>
       </c>
     </row>
     <row r="20">
@@ -8552,7 +8628,7 @@
         <v/>
       </c>
       <c r="F22" s="17" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="23">
@@ -8600,7 +8676,7 @@
         <v/>
       </c>
       <c r="F24" s="17" t="n">
-        <v>70</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25">
@@ -8624,7 +8700,7 @@
         <v/>
       </c>
       <c r="F25" s="17" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="26">
@@ -8648,7 +8724,7 @@
         <v/>
       </c>
       <c r="F26" s="17" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27">
@@ -8840,7 +8916,7 @@
         <v/>
       </c>
       <c r="F34" s="17" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35">
@@ -8973,7 +9049,7 @@
         <v/>
       </c>
       <c r="F4" s="27" t="n">
-        <v>1336</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="5">
@@ -8997,7 +9073,7 @@
         <v/>
       </c>
       <c r="F5" s="27" t="n">
-        <v>937</v>
+        <v>953</v>
       </c>
     </row>
     <row r="6">
@@ -9021,7 +9097,7 @@
         <v/>
       </c>
       <c r="F6" s="27" t="n">
-        <v>424</v>
+        <v>579</v>
       </c>
     </row>
     <row r="7">
@@ -9045,7 +9121,7 @@
         <v/>
       </c>
       <c r="F7" s="27" t="n">
-        <v>1471</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="8">
@@ -9069,7 +9145,7 @@
         <v/>
       </c>
       <c r="F8" s="37" t="n">
-        <v>603</v>
+        <v>626</v>
       </c>
     </row>
     <row r="9">
@@ -9093,7 +9169,7 @@
         <v/>
       </c>
       <c r="F9" s="37" t="n">
-        <v>84</v>
+        <v>170</v>
       </c>
     </row>
     <row r="10">
@@ -9141,7 +9217,7 @@
         <v/>
       </c>
       <c r="F11" s="37" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="12">
@@ -9165,7 +9241,7 @@
         <v/>
       </c>
       <c r="F12" s="37" t="n">
-        <v>639</v>
+        <v>746</v>
       </c>
     </row>
     <row r="13">
@@ -9213,7 +9289,7 @@
         <v/>
       </c>
       <c r="F14" s="37" t="n">
-        <v>538</v>
+        <v>578</v>
       </c>
     </row>
     <row r="15">
@@ -9237,7 +9313,7 @@
         <v/>
       </c>
       <c r="F15" s="37" t="n">
-        <v>248</v>
+        <v>307</v>
       </c>
     </row>
     <row r="16">
@@ -9261,7 +9337,7 @@
         <v/>
       </c>
       <c r="F16" s="37" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="17">
@@ -9285,7 +9361,7 @@
         <v/>
       </c>
       <c r="F17" s="37" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="18">
@@ -9309,7 +9385,7 @@
         <v/>
       </c>
       <c r="F18" s="37" t="n">
-        <v>131</v>
+        <v>188</v>
       </c>
     </row>
     <row r="19">
@@ -9333,7 +9409,7 @@
         <v/>
       </c>
       <c r="F19" s="37" t="n">
-        <v>258</v>
+        <v>325</v>
       </c>
     </row>
     <row r="20">
@@ -9357,7 +9433,7 @@
         <v/>
       </c>
       <c r="F20" s="37" t="n">
-        <v>30</v>
+        <v>146</v>
       </c>
     </row>
     <row r="21">
@@ -9381,7 +9457,7 @@
         <v/>
       </c>
       <c r="F21" s="37" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
     </row>
     <row r="22">
@@ -9429,7 +9505,7 @@
         <v/>
       </c>
       <c r="F23" s="37" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="24">
@@ -9477,7 +9553,7 @@
         <v/>
       </c>
       <c r="F25" s="37" t="n">
-        <v>268</v>
+        <v>342</v>
       </c>
     </row>
     <row r="26">
@@ -9501,7 +9577,7 @@
         <v/>
       </c>
       <c r="F26" s="37" t="n">
-        <v>487</v>
+        <v>554</v>
       </c>
     </row>
     <row r="27">
@@ -9597,7 +9673,7 @@
         <v/>
       </c>
       <c r="F30" s="37" t="n">
-        <v>68</v>
+        <v>73</v>
       </c>
     </row>
     <row r="31">
@@ -9621,7 +9697,7 @@
         <v/>
       </c>
       <c r="F31" s="37" t="n">
-        <v>8</v>
+        <v>32</v>
       </c>
     </row>
     <row r="32">
@@ -9645,7 +9721,7 @@
         <v/>
       </c>
       <c r="F32" s="37" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
     </row>
     <row r="33">
@@ -9717,7 +9793,7 @@
         <v/>
       </c>
       <c r="F35" s="37" t="n">
-        <v>36</v>
+        <v>61</v>
       </c>
     </row>
     <row r="36">
@@ -9741,7 +9817,7 @@
         <v/>
       </c>
       <c r="F36" s="37" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="37">
@@ -9789,7 +9865,7 @@
         <v/>
       </c>
       <c r="F38" s="37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="39">
@@ -9846,7 +9922,7 @@
           <t>합계</t>
         </is>
       </c>
-      <c r="B41" s="39" t="n"/>
+      <c r="B41" s="43" t="n"/>
       <c r="C41" s="40">
         <f>SUM(C3:C40)</f>
         <v/>
@@ -9946,7 +10022,7 @@
         <v/>
       </c>
       <c r="F3" s="27" t="n">
-        <v>1471</v>
+        <v>1578</v>
       </c>
     </row>
     <row r="4">
@@ -9970,7 +10046,7 @@
         <v/>
       </c>
       <c r="F4" s="27" t="n">
-        <v>1427</v>
+        <v>1456</v>
       </c>
     </row>
     <row r="5">
@@ -9994,7 +10070,7 @@
         <v/>
       </c>
       <c r="F5" s="27" t="n">
-        <v>1336</v>
+        <v>1413</v>
       </c>
     </row>
     <row r="6">
@@ -10018,7 +10094,7 @@
         <v/>
       </c>
       <c r="F6" s="27" t="n">
-        <v>251</v>
+        <v>254</v>
       </c>
     </row>
     <row r="7">
@@ -10042,7 +10118,7 @@
         <v/>
       </c>
       <c r="F7" s="27" t="n">
-        <v>603</v>
+        <v>626</v>
       </c>
     </row>
     <row r="8">
@@ -10090,7 +10166,7 @@
         <v/>
       </c>
       <c r="F9" s="37" t="n">
-        <v>487</v>
+        <v>554</v>
       </c>
     </row>
     <row r="10">
@@ -10114,7 +10190,7 @@
         <v/>
       </c>
       <c r="F10" s="37" t="n">
-        <v>639</v>
+        <v>746</v>
       </c>
     </row>
     <row r="11">
@@ -10138,7 +10214,7 @@
         <v/>
       </c>
       <c r="F11" s="37" t="n">
-        <v>538</v>
+        <v>578</v>
       </c>
     </row>
     <row r="12">
@@ -10162,7 +10238,7 @@
         <v/>
       </c>
       <c r="F12" s="37" t="n">
-        <v>268</v>
+        <v>342</v>
       </c>
     </row>
     <row r="13">
@@ -10258,7 +10334,7 @@
         <v/>
       </c>
       <c r="F16" s="37" t="n">
-        <v>937</v>
+        <v>953</v>
       </c>
     </row>
     <row r="17">
@@ -10282,7 +10358,7 @@
         <v/>
       </c>
       <c r="F17" s="37" t="n">
-        <v>153</v>
+        <v>171</v>
       </c>
     </row>
     <row r="18">
@@ -10306,7 +10382,7 @@
         <v/>
       </c>
       <c r="F18" s="37" t="n">
-        <v>31</v>
+        <v>42</v>
       </c>
     </row>
     <row r="19">
@@ -10354,7 +10430,7 @@
         <v/>
       </c>
       <c r="F20" s="37" t="n">
-        <v>293</v>
+        <v>294</v>
       </c>
     </row>
     <row r="21">
@@ -10402,7 +10478,7 @@
         <v/>
       </c>
       <c r="F22" s="37" t="n">
-        <v>248</v>
+        <v>307</v>
       </c>
     </row>
     <row r="23">
@@ -10426,7 +10502,7 @@
         <v/>
       </c>
       <c r="F23" s="37" t="n">
-        <v>12</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24">
@@ -10450,7 +10526,7 @@
         <v/>
       </c>
       <c r="F24" s="37" t="n">
-        <v>124</v>
+        <v>133</v>
       </c>
     </row>
     <row r="25">
@@ -10570,7 +10646,7 @@
         <v/>
       </c>
       <c r="F29" s="37" t="n">
-        <v>50</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30">
@@ -10666,7 +10742,7 @@
         <v/>
       </c>
       <c r="F33" s="37" t="n">
-        <v>92</v>
+        <v>97</v>
       </c>
     </row>
     <row r="34">
@@ -10714,7 +10790,7 @@
         <v/>
       </c>
       <c r="F35" s="37" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="36">
@@ -10738,7 +10814,7 @@
         <v/>
       </c>
       <c r="F36" s="37" t="n">
-        <v>55</v>
+        <v>69</v>
       </c>
     </row>
     <row r="37">
@@ -10762,7 +10838,7 @@
         <v/>
       </c>
       <c r="F37" s="37" t="n">
-        <v>27</v>
+        <v>38</v>
       </c>
     </row>
     <row r="38">
@@ -10771,7 +10847,7 @@
           <t>합계</t>
         </is>
       </c>
-      <c r="B38" s="39" t="n"/>
+      <c r="B38" s="43" t="n"/>
       <c r="C38" s="40">
         <f>SUM(C3:C37)</f>
         <v/>
@@ -10800,7 +10876,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -10811,55 +10887,908 @@
     <col width="13" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
-    <row r="1" ht="18" customHeight="1">
+    <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>2026년 8월 — 출하 데이터 없음</t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="28" customHeight="1">
-      <c r="A2" s="2" t="inlineStr">
+          <t>2026년 8월 출하현황 — 납품처별 출고량  (단위: 개)</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>순위</t>
         </is>
       </c>
-      <c r="B2" s="3" t="inlineStr">
+      <c r="B2" s="23" t="inlineStr">
         <is>
           <t>납품처명</t>
         </is>
       </c>
-      <c r="C2" s="2" t="inlineStr">
+      <c r="C2" s="23" t="inlineStr">
         <is>
           <t>8월 출고(개)</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="D2" s="23" t="inlineStr">
         <is>
           <t>월간비율(%)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="E2" s="23" t="inlineStr">
         <is>
           <t>누적비율(%)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr">
+      <c r="F2" s="23" t="inlineStr">
         <is>
           <t>연간합계(개)</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="22" t="inlineStr">
-        <is>
-          <t>해당 월 출하 데이터 없음</t>
-        </is>
+      <c r="A3" s="24" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="25" t="inlineStr">
+        <is>
+          <t>아신상사</t>
+        </is>
+      </c>
+      <c r="C3" s="27" t="n">
+        <v>155</v>
+      </c>
+      <c r="D3" s="28">
+        <f>C3/C$38</f>
+        <v/>
+      </c>
+      <c r="E3" s="28">
+        <f>D3</f>
+        <v/>
+      </c>
+      <c r="F3" s="27" t="n">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="24" t="n">
+        <v>2</v>
+      </c>
+      <c r="B4" s="25" t="inlineStr">
+        <is>
+          <t>지니툴(구로)_코고툴</t>
+        </is>
+      </c>
+      <c r="C4" s="27" t="n">
+        <v>116</v>
+      </c>
+      <c r="D4" s="28">
+        <f>C4/C$38</f>
+        <v/>
+      </c>
+      <c r="E4" s="28">
+        <f>E3+D4</f>
+        <v/>
+      </c>
+      <c r="F4" s="27" t="n">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="24" t="n">
+        <v>3</v>
+      </c>
+      <c r="B5" s="25" t="inlineStr">
+        <is>
+          <t>덕원종합상사</t>
+        </is>
+      </c>
+      <c r="C5" s="27" t="n">
+        <v>107</v>
+      </c>
+      <c r="D5" s="28">
+        <f>C5/C$38</f>
+        <v/>
+      </c>
+      <c r="E5" s="28">
+        <f>E4+D5</f>
+        <v/>
+      </c>
+      <c r="F5" s="27" t="n">
+        <v>746</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="24" t="n">
+        <v>4</v>
+      </c>
+      <c r="B6" s="25" t="inlineStr">
+        <is>
+          <t>원영공구(구,원영상사)</t>
+        </is>
+      </c>
+      <c r="C6" s="27" t="n">
+        <v>107</v>
+      </c>
+      <c r="D6" s="28">
+        <f>C6/C$38</f>
+        <v/>
+      </c>
+      <c r="E6" s="28">
+        <f>E5+D6</f>
+        <v/>
+      </c>
+      <c r="F6" s="27" t="n">
+        <v>1578</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="24" t="n">
+        <v>5</v>
+      </c>
+      <c r="B7" s="25" t="inlineStr">
+        <is>
+          <t>동명ENG-코고툴(재연마)</t>
+        </is>
+      </c>
+      <c r="C7" s="27" t="n">
+        <v>86</v>
+      </c>
+      <c r="D7" s="28">
+        <f>C7/C$38</f>
+        <v/>
+      </c>
+      <c r="E7" s="28">
+        <f>E6+D7</f>
+        <v/>
+      </c>
+      <c r="F7" s="27" t="n">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="24" t="n">
+        <v>6</v>
+      </c>
+      <c r="B8" s="25" t="inlineStr">
+        <is>
+          <t>건영테크(광주)</t>
+        </is>
+      </c>
+      <c r="C8" s="27" t="n">
+        <v>77</v>
+      </c>
+      <c r="D8" s="28">
+        <f>C8/C$38</f>
+        <v/>
+      </c>
+      <c r="E8" s="28">
+        <f>E7+D8</f>
+        <v/>
+      </c>
+      <c r="F8" s="27" t="n">
+        <v>1413</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="24" t="n">
+        <v>7</v>
+      </c>
+      <c r="B9" s="25" t="inlineStr">
+        <is>
+          <t>(주)공화공구</t>
+        </is>
+      </c>
+      <c r="C9" s="27" t="n">
+        <v>74</v>
+      </c>
+      <c r="D9" s="28">
+        <f>C9/C$38</f>
+        <v/>
+      </c>
+      <c r="E9" s="28">
+        <f>E8+D9</f>
+        <v/>
+      </c>
+      <c r="F9" s="27" t="n">
+        <v>342</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="24" t="n">
+        <v>8</v>
+      </c>
+      <c r="B10" s="25" t="inlineStr">
+        <is>
+          <t>신우툴링(남동)</t>
+        </is>
+      </c>
+      <c r="C10" s="27" t="n">
+        <v>67</v>
+      </c>
+      <c r="D10" s="28">
+        <f>C10/C$38</f>
+        <v/>
+      </c>
+      <c r="E10" s="28">
+        <f>E9+D10</f>
+        <v/>
+      </c>
+      <c r="F10" s="27" t="n">
+        <v>325</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="24" t="n">
+        <v>9</v>
+      </c>
+      <c r="B11" s="25" t="inlineStr">
+        <is>
+          <t>아이티공구</t>
+        </is>
+      </c>
+      <c r="C11" s="27" t="n">
+        <v>67</v>
+      </c>
+      <c r="D11" s="28">
+        <f>C11/C$38</f>
+        <v/>
+      </c>
+      <c r="E11" s="28">
+        <f>E10+D11</f>
+        <v/>
+      </c>
+      <c r="F11" s="27" t="n">
+        <v>554</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="24" t="n">
+        <v>10</v>
+      </c>
+      <c r="B12" s="25" t="inlineStr">
+        <is>
+          <t>반석공구</t>
+        </is>
+      </c>
+      <c r="C12" s="27" t="n">
+        <v>59</v>
+      </c>
+      <c r="D12" s="28">
+        <f>C12/C$38</f>
+        <v/>
+      </c>
+      <c r="E12" s="28">
+        <f>E11+D12</f>
+        <v/>
+      </c>
+      <c r="F12" s="27" t="n">
+        <v>307</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="24" t="n">
+        <v>11</v>
+      </c>
+      <c r="B13" s="25" t="inlineStr">
+        <is>
+          <t>핫몰드엔지니어링주식회사-코고툴(재연마)</t>
+        </is>
+      </c>
+      <c r="C13" s="27" t="n">
+        <v>57</v>
+      </c>
+      <c r="D13" s="28">
+        <f>C13/C$38</f>
+        <v/>
+      </c>
+      <c r="E13" s="28">
+        <f>E12+D13</f>
+        <v/>
+      </c>
+      <c r="F13" s="27" t="n">
+        <v>188</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="24" t="n">
+        <v>12</v>
+      </c>
+      <c r="B14" s="25" t="inlineStr">
+        <is>
+          <t>영우툴링(창성툴)</t>
+        </is>
+      </c>
+      <c r="C14" s="27" t="n">
+        <v>40</v>
+      </c>
+      <c r="D14" s="28">
+        <f>C14/C$38</f>
+        <v/>
+      </c>
+      <c r="E14" s="28">
+        <f>E13+D14</f>
+        <v/>
+      </c>
+      <c r="F14" s="27" t="n">
+        <v>578</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="24" t="n">
+        <v>13</v>
+      </c>
+      <c r="B15" s="25" t="inlineStr">
+        <is>
+          <t>초경툴(구,성민TOOL)-코고툴</t>
+        </is>
+      </c>
+      <c r="C15" s="27" t="n">
+        <v>29</v>
+      </c>
+      <c r="D15" s="28">
+        <f>C15/C$38</f>
+        <v/>
+      </c>
+      <c r="E15" s="28">
+        <f>E14+D15</f>
+        <v/>
+      </c>
+      <c r="F15" s="27" t="n">
+        <v>1456</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="24" t="n">
+        <v>14</v>
+      </c>
+      <c r="B16" s="25" t="inlineStr">
+        <is>
+          <t>공구백화점(미산동)</t>
+        </is>
+      </c>
+      <c r="C16" s="27" t="n">
+        <v>25</v>
+      </c>
+      <c r="D16" s="28">
+        <f>C16/C$38</f>
+        <v/>
+      </c>
+      <c r="E16" s="28">
+        <f>E15+D16</f>
+        <v/>
+      </c>
+      <c r="F16" s="27" t="n">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="24" t="n">
+        <v>15</v>
+      </c>
+      <c r="B17" s="25" t="inlineStr">
+        <is>
+          <t>영호종합공구(향남)</t>
+        </is>
+      </c>
+      <c r="C17" s="27" t="n">
+        <v>24</v>
+      </c>
+      <c r="D17" s="28">
+        <f>C17/C$38</f>
+        <v/>
+      </c>
+      <c r="E17" s="28">
+        <f>E16+D17</f>
+        <v/>
+      </c>
+      <c r="F17" s="27" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="24" t="n">
+        <v>16</v>
+      </c>
+      <c r="B18" s="25" t="inlineStr">
+        <is>
+          <t>연성기공(주)</t>
+        </is>
+      </c>
+      <c r="C18" s="27" t="n">
+        <v>23</v>
+      </c>
+      <c r="D18" s="28">
+        <f>C18/C$38</f>
+        <v/>
+      </c>
+      <c r="E18" s="28">
+        <f>E17+D18</f>
+        <v/>
+      </c>
+      <c r="F18" s="27" t="n">
+        <v>626</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="24" t="n">
+        <v>17</v>
+      </c>
+      <c r="B19" s="25" t="inlineStr">
+        <is>
+          <t>(주)정원테크</t>
+        </is>
+      </c>
+      <c r="C19" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="D19" s="28">
+        <f>C19/C$38</f>
+        <v/>
+      </c>
+      <c r="E19" s="28">
+        <f>E18+D19</f>
+        <v/>
+      </c>
+      <c r="F19" s="27" t="n">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="24" t="n">
+        <v>18</v>
+      </c>
+      <c r="B20" s="25" t="inlineStr">
+        <is>
+          <t>신우툴스</t>
+        </is>
+      </c>
+      <c r="C20" s="27" t="n">
+        <v>20</v>
+      </c>
+      <c r="D20" s="28">
+        <f>C20/C$38</f>
+        <v/>
+      </c>
+      <c r="E20" s="28">
+        <f>E19+D20</f>
+        <v/>
+      </c>
+      <c r="F20" s="27" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="24" t="n">
+        <v>19</v>
+      </c>
+      <c r="B21" s="25" t="inlineStr">
+        <is>
+          <t>서림툴링</t>
+        </is>
+      </c>
+      <c r="C21" s="27" t="n">
+        <v>18</v>
+      </c>
+      <c r="D21" s="28">
+        <f>C21/C$38</f>
+        <v/>
+      </c>
+      <c r="E21" s="28">
+        <f>E20+D21</f>
+        <v/>
+      </c>
+      <c r="F21" s="27" t="n">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="24" t="n">
+        <v>20</v>
+      </c>
+      <c r="B22" s="25" t="inlineStr">
+        <is>
+          <t>강민툴링(비봉)</t>
+        </is>
+      </c>
+      <c r="C22" s="27" t="n">
+        <v>16</v>
+      </c>
+      <c r="D22" s="28">
+        <f>C22/C$38</f>
+        <v/>
+      </c>
+      <c r="E22" s="28">
+        <f>E21+D22</f>
+        <v/>
+      </c>
+      <c r="F22" s="27" t="n">
+        <v>953</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="24" t="n">
+        <v>21</v>
+      </c>
+      <c r="B23" s="25" t="inlineStr">
+        <is>
+          <t>(주)전진공구</t>
+        </is>
+      </c>
+      <c r="C23" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="D23" s="28">
+        <f>C23/C$38</f>
+        <v/>
+      </c>
+      <c r="E23" s="28">
+        <f>E22+D23</f>
+        <v/>
+      </c>
+      <c r="F23" s="27" t="n">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="24" t="n">
+        <v>22</v>
+      </c>
+      <c r="B24" s="25" t="inlineStr">
+        <is>
+          <t>맨날툴이야</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="n">
+        <v>14</v>
+      </c>
+      <c r="D24" s="28">
+        <f>C24/C$38</f>
+        <v/>
+      </c>
+      <c r="E24" s="28">
+        <f>E23+D24</f>
+        <v/>
+      </c>
+      <c r="F24" s="27" t="n">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="24" t="n">
+        <v>23</v>
+      </c>
+      <c r="B25" s="25" t="inlineStr">
+        <is>
+          <t>(주)바로공구(정남)</t>
+        </is>
+      </c>
+      <c r="C25" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="D25" s="28">
+        <f>C25/C$38</f>
+        <v/>
+      </c>
+      <c r="E25" s="28">
+        <f>E24+D25</f>
+        <v/>
+      </c>
+      <c r="F25" s="27" t="n">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="24" t="n">
+        <v>24</v>
+      </c>
+      <c r="B26" s="25" t="inlineStr">
+        <is>
+          <t>유진상사(문래)</t>
+        </is>
+      </c>
+      <c r="C26" s="27" t="n">
+        <v>11</v>
+      </c>
+      <c r="D26" s="28">
+        <f>C26/C$38</f>
+        <v/>
+      </c>
+      <c r="E26" s="28">
+        <f>E25+D26</f>
+        <v/>
+      </c>
+      <c r="F26" s="27" t="n">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="24" t="n">
+        <v>25</v>
+      </c>
+      <c r="B27" s="25" t="inlineStr">
+        <is>
+          <t>아시아툴링</t>
+        </is>
+      </c>
+      <c r="C27" s="27" t="n">
+        <v>10</v>
+      </c>
+      <c r="D27" s="28">
+        <f>C27/C$38</f>
+        <v/>
+      </c>
+      <c r="E27" s="28">
+        <f>E26+D27</f>
+        <v/>
+      </c>
+      <c r="F27" s="27" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="24" t="n">
+        <v>26</v>
+      </c>
+      <c r="B28" s="25" t="inlineStr">
+        <is>
+          <t>대우툴링</t>
+        </is>
+      </c>
+      <c r="C28" s="27" t="n">
+        <v>9</v>
+      </c>
+      <c r="D28" s="28">
+        <f>C28/C$38</f>
+        <v/>
+      </c>
+      <c r="E28" s="28">
+        <f>E27+D28</f>
+        <v/>
+      </c>
+      <c r="F28" s="27" t="n">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="24" t="n">
+        <v>27</v>
+      </c>
+      <c r="B29" s="25" t="inlineStr">
+        <is>
+          <t>광진테크</t>
+        </is>
+      </c>
+      <c r="C29" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D29" s="28">
+        <f>C29/C$38</f>
+        <v/>
+      </c>
+      <c r="E29" s="28">
+        <f>E28+D29</f>
+        <v/>
+      </c>
+      <c r="F29" s="27" t="n">
+        <v>73</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="24" t="n">
+        <v>28</v>
+      </c>
+      <c r="B30" s="25" t="inlineStr">
+        <is>
+          <t>유성상공사</t>
+        </is>
+      </c>
+      <c r="C30" s="27" t="n">
+        <v>5</v>
+      </c>
+      <c r="D30" s="28">
+        <f>C30/C$38</f>
+        <v/>
+      </c>
+      <c r="E30" s="28">
+        <f>E29+D30</f>
+        <v/>
+      </c>
+      <c r="F30" s="27" t="n">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="24" t="n">
+        <v>29</v>
+      </c>
+      <c r="B31" s="25" t="inlineStr">
+        <is>
+          <t>(주)성환공구</t>
+        </is>
+      </c>
+      <c r="C31" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D31" s="28">
+        <f>C31/C$38</f>
+        <v/>
+      </c>
+      <c r="E31" s="28">
+        <f>E30+D31</f>
+        <v/>
+      </c>
+      <c r="F31" s="27" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="24" t="n">
+        <v>30</v>
+      </c>
+      <c r="B32" s="25" t="inlineStr">
+        <is>
+          <t>대양공구(인천)</t>
+        </is>
+      </c>
+      <c r="C32" s="27" t="n">
+        <v>4</v>
+      </c>
+      <c r="D32" s="28">
+        <f>C32/C$38</f>
+        <v/>
+      </c>
+      <c r="E32" s="28">
+        <f>E31+D32</f>
+        <v/>
+      </c>
+      <c r="F32" s="27" t="n">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="24" t="n">
+        <v>31</v>
+      </c>
+      <c r="B33" s="25" t="inlineStr">
+        <is>
+          <t>대륙기계공구</t>
+        </is>
+      </c>
+      <c r="C33" s="27" t="n">
+        <v>3</v>
+      </c>
+      <c r="D33" s="28">
+        <f>C33/C$38</f>
+        <v/>
+      </c>
+      <c r="E33" s="28">
+        <f>E32+D33</f>
+        <v/>
+      </c>
+      <c r="F33" s="27" t="n">
+        <v>254</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="24" t="n">
+        <v>32</v>
+      </c>
+      <c r="B34" s="25" t="inlineStr">
+        <is>
+          <t>웰크리에이트-코고툴(재연마)</t>
+        </is>
+      </c>
+      <c r="C34" s="27" t="n">
+        <v>2</v>
+      </c>
+      <c r="D34" s="28">
+        <f>C34/C$38</f>
+        <v/>
+      </c>
+      <c r="E34" s="28">
+        <f>E33+D34</f>
+        <v/>
+      </c>
+      <c r="F34" s="27" t="n">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="24" t="n">
+        <v>33</v>
+      </c>
+      <c r="B35" s="25" t="inlineStr">
+        <is>
+          <t>(주)일등정밀공구(안산)</t>
+        </is>
+      </c>
+      <c r="C35" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D35" s="28">
+        <f>C35/C$38</f>
+        <v/>
+      </c>
+      <c r="E35" s="28">
+        <f>E34+D35</f>
+        <v/>
+      </c>
+      <c r="F35" s="27" t="n">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="24" t="n">
+        <v>34</v>
+      </c>
+      <c r="B36" s="25" t="inlineStr">
+        <is>
+          <t>대한초경공구</t>
+        </is>
+      </c>
+      <c r="C36" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="28">
+        <f>C36/C$38</f>
+        <v/>
+      </c>
+      <c r="E36" s="28">
+        <f>E35+D36</f>
+        <v/>
+      </c>
+      <c r="F36" s="27" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="24" t="n">
+        <v>35</v>
+      </c>
+      <c r="B37" s="25" t="inlineStr">
+        <is>
+          <t>왕삼아공구</t>
+        </is>
+      </c>
+      <c r="C37" s="27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D37" s="28">
+        <f>C37/C$38</f>
+        <v/>
+      </c>
+      <c r="E37" s="28">
+        <f>E36+D37</f>
+        <v/>
+      </c>
+      <c r="F37" s="27" t="n">
+        <v>294</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="39" t="inlineStr">
+        <is>
+          <t>합계</t>
+        </is>
+      </c>
+      <c r="B38" s="43" t="n"/>
+      <c r="C38" s="40">
+        <f>SUM(C3:C37)</f>
+        <v/>
+      </c>
+      <c r="D38" s="41" t="n">
+        <v>1</v>
+      </c>
+      <c r="E38" s="39" t="n"/>
+      <c r="F38" s="40">
+        <f>SUM(F3:F37)</f>
+        <v/>
       </c>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A3:F3"/>
+    <mergeCell ref="A38:B38"/>
     <mergeCell ref="A1:F1"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
